--- a/database/event/8036/event_8036_evp_summary.xlsx
+++ b/database/event/8036/event_8036_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>10.9173</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5.6805</v>
       </c>
       <c r="D2" t="n">
         <v>3.989</v>
@@ -545,7 +545,7 @@
         <v>9.648199999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.0202</v>
       </c>
       <c r="D3" t="n">
         <v>3.4763</v>
@@ -591,7 +591,7 @@
         <v>8.489000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.417</v>
       </c>
       <c r="D4" t="n">
         <v>3.008</v>
@@ -637,7 +637,7 @@
         <v>7.1558</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.7233</v>
       </c>
       <c r="D5" t="n">
         <v>2.4694</v>
@@ -683,7 +683,7 @@
         <v>5.7428</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>2.9881</v>
       </c>
       <c r="D6" t="n">
         <v>1.8986</v>
@@ -729,7 +729,7 @@
         <v>5.6788</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.9548</v>
       </c>
       <c r="D7" t="n">
         <v>1.8727</v>
@@ -775,7 +775,7 @@
         <v>5.675</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.9528</v>
       </c>
       <c r="D8" t="n">
         <v>1.8712</v>
@@ -821,7 +821,7 @@
         <v>5.2118</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.7118</v>
       </c>
       <c r="D9" t="n">
         <v>1.6841</v>
@@ -867,7 +867,7 @@
         <v>4.6793</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.4347</v>
       </c>
       <c r="D10" t="n">
         <v>1.469</v>
@@ -913,7 +913,7 @@
         <v>4.2067</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.1888</v>
       </c>
       <c r="D11" t="n">
         <v>1.2781</v>
@@ -959,7 +959,7 @@
         <v>4.1818</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.1759</v>
       </c>
       <c r="D12" t="n">
         <v>1.268</v>
@@ -1005,7 +1005,7 @@
         <v>3.9819</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.0719</v>
       </c>
       <c r="D13" t="n">
         <v>1.1872</v>
@@ -1051,7 +1051,7 @@
         <v>3.9638</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.0624</v>
       </c>
       <c r="D14" t="n">
         <v>1.1799</v>
@@ -1097,7 +1097,7 @@
         <v>3.8105</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.9827</v>
       </c>
       <c r="D15" t="n">
         <v>1.118</v>
@@ -1143,7 +1143,7 @@
         <v>3.7811</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.9674</v>
       </c>
       <c r="D16" t="n">
         <v>1.1061</v>
@@ -1189,7 +1189,7 @@
         <v>3.5061</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.8243</v>
       </c>
       <c r="D17" t="n">
         <v>0.995</v>
@@ -1235,7 +1235,7 @@
         <v>3.3159</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.7253</v>
       </c>
       <c r="D18" t="n">
         <v>0.9182</v>
@@ -1281,7 +1281,7 @@
         <v>3.2385</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.6851</v>
       </c>
       <c r="D19" t="n">
         <v>0.8869</v>
@@ -1327,7 +1327,7 @@
         <v>2.8065</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.4603</v>
       </c>
       <c r="D20" t="n">
         <v>0.7124</v>
@@ -1373,7 +1373,7 @@
         <v>2.4249</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.2617</v>
       </c>
       <c r="D21" t="n">
         <v>0.5582</v>
@@ -1419,7 +1419,7 @@
         <v>2.4125</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.2553</v>
       </c>
       <c r="D22" t="n">
         <v>0.5532</v>
@@ -1465,7 +1465,7 @@
         <v>2.3636</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.2298</v>
       </c>
       <c r="D23" t="n">
         <v>0.5335</v>
@@ -1511,7 +1511,7 @@
         <v>2.1632</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.1256</v>
       </c>
       <c r="D24" t="n">
         <v>0.4525</v>
@@ -1557,7 +1557,7 @@
         <v>1.9014</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.9893</v>
       </c>
       <c r="D25" t="n">
         <v>0.3468</v>
@@ -1603,7 +1603,7 @@
         <v>1.8109</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.9422</v>
       </c>
       <c r="D26" t="n">
         <v>0.3102</v>
@@ -1649,7 +1649,7 @@
         <v>1.7888</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.9307</v>
       </c>
       <c r="D27" t="n">
         <v>0.3013</v>
@@ -1695,7 +1695,7 @@
         <v>1.7235</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.8968</v>
       </c>
       <c r="D28" t="n">
         <v>0.2749</v>
@@ -1741,7 +1741,7 @@
         <v>1.512</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.7867</v>
       </c>
       <c r="D29" t="n">
         <v>0.1895</v>
@@ -1787,7 +1787,7 @@
         <v>1.235</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="D30" t="n">
         <v>0.0776</v>
@@ -1833,7 +1833,7 @@
         <v>1.1688</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.6082</v>
       </c>
       <c r="D31" t="n">
         <v>0.0508</v>
@@ -1879,7 +1879,7 @@
         <v>1.0747</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.5592</v>
       </c>
       <c r="D32" t="n">
         <v>0.0128</v>
@@ -1925,7 +1925,7 @@
         <v>1.0397</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="D33" t="n">
         <v>-0.0013</v>
@@ -1971,7 +1971,7 @@
         <v>0.9524</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.4956</v>
       </c>
       <c r="D34" t="n">
         <v>-0.0366</v>
@@ -2017,7 +2017,7 @@
         <v>0.906</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.4714</v>
       </c>
       <c r="D35" t="n">
         <v>-0.0554</v>
@@ -2063,7 +2063,7 @@
         <v>0.9056999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.4713</v>
       </c>
       <c r="D36" t="n">
         <v>-0.0555</v>
@@ -2109,7 +2109,7 @@
         <v>0.8843</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.4601</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0641</v>
@@ -2155,7 +2155,7 @@
         <v>0.8837</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.4598</v>
       </c>
       <c r="D38" t="n">
         <v>-0.0644</v>
@@ -2201,7 +2201,7 @@
         <v>0.8809</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.4584</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0655</v>
@@ -2247,7 +2247,7 @@
         <v>0.8505</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4425</v>
       </c>
       <c r="D40" t="n">
         <v>-0.07779999999999999</v>
@@ -2293,7 +2293,7 @@
         <v>0.8342000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.4341</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0844</v>
@@ -2339,7 +2339,7 @@
         <v>0.7369</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.3834</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1237</v>
@@ -2385,7 +2385,7 @@
         <v>0.6876</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3578</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1436</v>
@@ -2431,7 +2431,7 @@
         <v>0.4471</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2326</v>
       </c>
       <c r="D44" t="n">
         <v>-0.2407</v>
@@ -2477,7 +2477,7 @@
         <v>0.3791</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.1973</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2682</v>
@@ -2523,7 +2523,7 @@
         <v>0.3465</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1803</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2814</v>
@@ -2569,7 +2569,7 @@
         <v>0.2616</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.1361</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3157</v>
@@ -2615,7 +2615,7 @@
         <v>0.0501</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0261</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4011</v>
@@ -2661,7 +2661,7 @@
         <v>0.0359</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0187</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4069</v>
@@ -2707,7 +2707,7 @@
         <v>-0.0307</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.016</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4338</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0318</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0165</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4342</v>
@@ -2799,7 +2799,7 @@
         <v>-0.0464</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0241</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4401</v>
@@ -2845,7 +2845,7 @@
         <v>-0.0575</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0299</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4446</v>
@@ -2891,7 +2891,7 @@
         <v>-0.1198</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.0623</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4698</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2169</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1129</v>
       </c>
       <c r="D55" t="n">
         <v>-0.509</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2319</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1207</v>
       </c>
       <c r="D56" t="n">
         <v>-0.515</v>
@@ -3029,7 +3029,7 @@
         <v>-0.2511</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1307</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5228</v>
@@ -3075,7 +3075,7 @@
         <v>-0.4021</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2092</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5838</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4317</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2246</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5958</v>
@@ -3167,7 +3167,7 @@
         <v>-0.4505</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2344</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6034</v>
@@ -3213,7 +3213,7 @@
         <v>-0.4617</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.2402</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6079</v>
@@ -3259,7 +3259,7 @@
         <v>-0.4796</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.2495</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6151</v>
@@ -3305,7 +3305,7 @@
         <v>-0.4848</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.2523</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6172</v>
@@ -3351,7 +3351,7 @@
         <v>-0.5206</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.2709</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6317</v>
@@ -3397,7 +3397,7 @@
         <v>-0.5881999999999999</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.3061</v>
       </c>
       <c r="D65" t="n">
         <v>-0.659</v>
@@ -3443,7 +3443,7 @@
         <v>-0.625</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.3252</v>
       </c>
       <c r="D66" t="n">
         <v>-0.6738</v>
@@ -3489,7 +3489,7 @@
         <v>-0.6586</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.3427</v>
       </c>
       <c r="D67" t="n">
         <v>-0.6874</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9360000000000001</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.487</v>
       </c>
       <c r="D68" t="n">
         <v>-0.7995</v>
@@ -3581,7 +3581,7 @@
         <v>-0.9593</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.4991</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8089</v>
@@ -3627,7 +3627,7 @@
         <v>-0.9782999999999999</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.509</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8166</v>
@@ -3673,7 +3673,7 @@
         <v>-1.0297</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="D71" t="n">
         <v>-0.8373</v>
@@ -3719,7 +3719,7 @@
         <v>-1.0426</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.5425</v>
       </c>
       <c r="D72" t="n">
         <v>-0.8425</v>
@@ -3765,7 +3765,7 @@
         <v>-1.0982</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.5714</v>
       </c>
       <c r="D73" t="n">
         <v>-0.865</v>
@@ -3811,7 +3811,7 @@
         <v>-1.6208</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.8433</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0761</v>
@@ -3857,7 +3857,7 @@
         <v>-1.841</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.9579</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1651</v>
@@ -3903,7 +3903,7 @@
         <v>-2</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0406</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2293</v>
@@ -3949,7 +3949,7 @@
         <v>-2.7218</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.4162</v>
       </c>
       <c r="D77" t="n">
         <v>-1.5209</v>
@@ -3995,7 +3995,7 @@
         <v>-3.0555</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.5898</v>
       </c>
       <c r="D78" t="n">
         <v>-1.6557</v>
@@ -4041,7 +4041,7 @@
         <v>-3.3648</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.7508</v>
       </c>
       <c r="D79" t="n">
         <v>-1.7807</v>
@@ -4087,7 +4087,7 @@
         <v>-4.3724</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.275</v>
       </c>
       <c r="D80" t="n">
         <v>-2.1877</v>
@@ -4133,7 +4133,7 @@
         <v>-4.4155</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.2975</v>
       </c>
       <c r="D81" t="n">
         <v>-2.2051</v>

--- a/database/event/8036/event_8036_evp_summary.xlsx
+++ b/database/event/8036/event_8036_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>5.6805</v>
       </c>
       <c r="D2" t="n">
-        <v>3.989</v>
+        <v>3.9055</v>
       </c>
       <c r="E2" t="n">
         <v>10.9173</v>
@@ -548,7 +548,7 @@
         <v>5.0202</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4763</v>
+        <v>3.3999</v>
       </c>
       <c r="E3" t="n">
         <v>9.648199999999999</v>
@@ -594,7 +594,7 @@
         <v>4.417</v>
       </c>
       <c r="D4" t="n">
-        <v>3.008</v>
+        <v>2.9381</v>
       </c>
       <c r="E4" t="n">
         <v>8.489000000000001</v>
@@ -640,7 +640,7 @@
         <v>3.7233</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4694</v>
+        <v>2.407</v>
       </c>
       <c r="E5" t="n">
         <v>7.1558</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7428</v>
+        <v>5.7231</v>
       </c>
       <c r="C6" t="n">
-        <v>2.9881</v>
+        <v>2.9778</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8986</v>
+        <v>1.8362</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7428</v>
+        <v>5.7231</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1153</v>
+        <v>4.0956</v>
       </c>
       <c r="G6" t="n">
         <v>1.6275</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1498</v>
+        <v>4.1189</v>
       </c>
       <c r="I6" t="n">
         <v>4.1885</v>
@@ -732,7 +732,7 @@
         <v>2.9548</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8727</v>
+        <v>1.8185</v>
       </c>
       <c r="E7" t="n">
         <v>5.6788</v>
@@ -778,7 +778,7 @@
         <v>2.9528</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8712</v>
+        <v>1.817</v>
       </c>
       <c r="E8" t="n">
         <v>5.675</v>
@@ -824,7 +824,7 @@
         <v>2.7118</v>
       </c>
       <c r="D9" t="n">
-        <v>1.6841</v>
+        <v>1.6325</v>
       </c>
       <c r="E9" t="n">
         <v>5.2118</v>
@@ -870,7 +870,7 @@
         <v>2.4347</v>
       </c>
       <c r="D10" t="n">
-        <v>1.469</v>
+        <v>1.4203</v>
       </c>
       <c r="E10" t="n">
         <v>4.6793</v>
@@ -916,7 +916,7 @@
         <v>2.1888</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2781</v>
+        <v>1.232</v>
       </c>
       <c r="E11" t="n">
         <v>4.2067</v>
@@ -962,7 +962,7 @@
         <v>2.1759</v>
       </c>
       <c r="D12" t="n">
-        <v>1.268</v>
+        <v>1.2221</v>
       </c>
       <c r="E12" t="n">
         <v>4.1818</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.9819</v>
+        <v>3.9638</v>
       </c>
       <c r="C13" t="n">
-        <v>2.0719</v>
+        <v>2.0624</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1872</v>
+        <v>1.1353</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9819</v>
+        <v>3.9638</v>
       </c>
       <c r="F13" t="n">
-        <v>4.9819</v>
+        <v>3.9638</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5086</v>
+        <v>3.9638</v>
       </c>
       <c r="I13" t="n">
-        <v>5.56</v>
+        <v>3.9638</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.56</v>
+        <v>3.9638</v>
       </c>
       <c r="N13" t="n">
-        <v>235</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9638</v>
+        <v>3.9558</v>
       </c>
       <c r="C14" t="n">
-        <v>2.0624</v>
+        <v>2.0583</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1799</v>
+        <v>1.1321</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9638</v>
+        <v>3.9558</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9638</v>
+        <v>4.9558</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9638</v>
+        <v>5.4676</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9638</v>
+        <v>5.56</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K14" t="n">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9638</v>
+        <v>4.56</v>
       </c>
       <c r="N14" t="n">
-        <v>167</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
@@ -1100,7 +1100,7 @@
         <v>1.9827</v>
       </c>
       <c r="D15" t="n">
-        <v>1.118</v>
+        <v>1.0742</v>
       </c>
       <c r="E15" t="n">
         <v>3.8105</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.7811</v>
+        <v>3.7592</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9674</v>
+        <v>1.956</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1061</v>
+        <v>1.0538</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7811</v>
+        <v>3.7592</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9479</v>
+        <v>2.926</v>
       </c>
       <c r="G16" t="n">
         <v>0.8332000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9479</v>
+        <v>2.926</v>
       </c>
       <c r="I16" t="n">
         <v>2.9754</v>
@@ -1192,7 +1192,7 @@
         <v>1.8243</v>
       </c>
       <c r="D17" t="n">
-        <v>0.995</v>
+        <v>0.9529</v>
       </c>
       <c r="E17" t="n">
         <v>3.5061</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3159</v>
+        <v>3.2947</v>
       </c>
       <c r="C18" t="n">
-        <v>1.7253</v>
+        <v>1.7143</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9182</v>
+        <v>0.8687</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3159</v>
+        <v>3.2947</v>
       </c>
       <c r="F18" t="n">
-        <v>4.3159</v>
+        <v>4.2947</v>
       </c>
       <c r="G18" t="n">
         <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4642</v>
+        <v>4.431</v>
       </c>
       <c r="I18" t="n">
         <v>4.5059</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.2385</v>
+        <v>3.2144</v>
       </c>
       <c r="C19" t="n">
-        <v>1.6851</v>
+        <v>1.6725</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8869</v>
+        <v>0.8367</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2385</v>
+        <v>3.2144</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2385</v>
+        <v>3.2144</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2385</v>
+        <v>3.2144</v>
       </c>
       <c r="I19" t="n">
         <v>3.2687</v>
@@ -1330,7 +1330,7 @@
         <v>1.4603</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7124</v>
+        <v>0.6742</v>
       </c>
       <c r="E20" t="n">
         <v>2.8065</v>
@@ -1376,7 +1376,7 @@
         <v>1.2617</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5582</v>
+        <v>0.5222</v>
       </c>
       <c r="E21" t="n">
         <v>2.4249</v>
@@ -1422,7 +1422,7 @@
         <v>1.2553</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5532</v>
+        <v>0.5172</v>
       </c>
       <c r="E22" t="n">
         <v>2.4125</v>
@@ -1468,7 +1468,7 @@
         <v>1.2298</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5335</v>
+        <v>0.4977</v>
       </c>
       <c r="E23" t="n">
         <v>2.3636</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1632</v>
+        <v>2.1471</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1256</v>
+        <v>1.1172</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4525</v>
+        <v>0.4115</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1632</v>
+        <v>2.1471</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1632</v>
+        <v>2.1471</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.1632</v>
+        <v>2.1471</v>
       </c>
       <c r="I24" t="n">
         <v>2.1834</v>
@@ -1560,7 +1560,7 @@
         <v>0.9893</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3468</v>
+        <v>0.3136</v>
       </c>
       <c r="E25" t="n">
         <v>1.9014</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.8109</v>
+        <v>1.8013</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9422</v>
+        <v>0.9373</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3102</v>
+        <v>0.2737</v>
       </c>
       <c r="E26" t="n">
-        <v>1.8109</v>
+        <v>1.8013</v>
       </c>
       <c r="F26" t="n">
-        <v>1.292</v>
+        <v>1.2824</v>
       </c>
       <c r="G26" t="n">
         <v>0.5189</v>
       </c>
       <c r="H26" t="n">
-        <v>1.292</v>
+        <v>1.2824</v>
       </c>
       <c r="I26" t="n">
         <v>1.3041</v>
@@ -1652,7 +1652,7 @@
         <v>0.9307</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3013</v>
+        <v>0.2687</v>
       </c>
       <c r="E27" t="n">
         <v>1.7888</v>
@@ -1698,7 +1698,7 @@
         <v>0.8968</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2749</v>
+        <v>0.2427</v>
       </c>
       <c r="E28" t="n">
         <v>1.7235</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.512</v>
+        <v>1.5007</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7867</v>
+        <v>0.7808</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1895</v>
+        <v>0.154</v>
       </c>
       <c r="E29" t="n">
-        <v>1.512</v>
+        <v>1.5007</v>
       </c>
       <c r="F29" t="n">
-        <v>1.512</v>
+        <v>1.5007</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.512</v>
+        <v>1.5007</v>
       </c>
       <c r="I29" t="n">
         <v>1.5261</v>
@@ -1790,7 +1790,7 @@
         <v>0.6425999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0776</v>
+        <v>0.0481</v>
       </c>
       <c r="E30" t="n">
         <v>1.235</v>
@@ -1836,7 +1836,7 @@
         <v>0.6082</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0508</v>
+        <v>0.0217</v>
       </c>
       <c r="E31" t="n">
         <v>1.1688</v>
@@ -1882,7 +1882,7 @@
         <v>0.5592</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0128</v>
+        <v>-0.0157</v>
       </c>
       <c r="E32" t="n">
         <v>1.0747</v>
@@ -1928,7 +1928,7 @@
         <v>0.541</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0013</v>
+        <v>-0.0297</v>
       </c>
       <c r="E33" t="n">
         <v>1.0397</v>
@@ -1974,7 +1974,7 @@
         <v>0.4956</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0366</v>
+        <v>-0.0645</v>
       </c>
       <c r="E34" t="n">
         <v>0.9524</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.906</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>0.4714</v>
+        <v>0.4713</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0554</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.906</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>0.906</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.906</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>0.9145</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>251</v>
+        <v>191</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.9145</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>251</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8993</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4713</v>
+        <v>0.4679</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0555</v>
+        <v>-0.0856</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8993</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8993</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.8993</v>
       </c>
       <c r="I36" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9145</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9145</v>
       </c>
       <c r="N36" t="n">
-        <v>191</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37">
@@ -2112,7 +2112,7 @@
         <v>0.4601</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0641</v>
+        <v>-0.0916</v>
       </c>
       <c r="E37" t="n">
         <v>0.8843</v>
@@ -2158,7 +2158,7 @@
         <v>0.4598</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0644</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="E38" t="n">
         <v>0.8837</v>
@@ -2204,7 +2204,7 @@
         <v>0.4584</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0655</v>
+        <v>-0.093</v>
       </c>
       <c r="E39" t="n">
         <v>0.8809</v>
@@ -2250,7 +2250,7 @@
         <v>0.4425</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.07779999999999999</v>
+        <v>-0.1051</v>
       </c>
       <c r="E40" t="n">
         <v>0.8505</v>
@@ -2296,7 +2296,7 @@
         <v>0.4341</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0844</v>
+        <v>-0.1116</v>
       </c>
       <c r="E41" t="n">
         <v>0.8342000000000001</v>
@@ -2342,7 +2342,7 @@
         <v>0.3834</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1237</v>
+        <v>-0.1503</v>
       </c>
       <c r="E42" t="n">
         <v>0.7369</v>
@@ -2388,7 +2388,7 @@
         <v>0.3578</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1436</v>
+        <v>-0.17</v>
       </c>
       <c r="E43" t="n">
         <v>0.6876</v>
@@ -2434,7 +2434,7 @@
         <v>0.2326</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2407</v>
+        <v>-0.2658</v>
       </c>
       <c r="E44" t="n">
         <v>0.4471</v>
@@ -2480,7 +2480,7 @@
         <v>0.1973</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2682</v>
+        <v>-0.2929</v>
       </c>
       <c r="E45" t="n">
         <v>0.3791</v>
@@ -2526,7 +2526,7 @@
         <v>0.1803</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2814</v>
+        <v>-0.3059</v>
       </c>
       <c r="E46" t="n">
         <v>0.3465</v>
@@ -2572,7 +2572,7 @@
         <v>0.1361</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3157</v>
+        <v>-0.3397</v>
       </c>
       <c r="E47" t="n">
         <v>0.2616</v>
@@ -2618,7 +2618,7 @@
         <v>0.0261</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4011</v>
+        <v>-0.424</v>
       </c>
       <c r="E48" t="n">
         <v>0.0501</v>
@@ -2664,7 +2664,7 @@
         <v>0.0187</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4069</v>
+        <v>-0.4296</v>
       </c>
       <c r="E49" t="n">
         <v>0.0359</v>
@@ -2710,7 +2710,7 @@
         <v>-0.016</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4338</v>
+        <v>-0.4561</v>
       </c>
       <c r="E50" t="n">
         <v>-0.0307</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0165</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4342</v>
+        <v>-0.4566</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0318</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.0464</v>
+        <v>-0.0535</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0241</v>
+        <v>-0.0278</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4401</v>
+        <v>-0.4652</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.0464</v>
+        <v>-0.0535</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9536</v>
+        <v>0.9465</v>
       </c>
       <c r="G52" t="n">
         <v>-1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9536</v>
+        <v>0.9465</v>
       </c>
       <c r="I52" t="n">
         <v>0.9625</v>
@@ -2848,7 +2848,7 @@
         <v>-0.0299</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4446</v>
+        <v>-0.4668</v>
       </c>
       <c r="E53" t="n">
         <v>-0.0575</v>
@@ -2894,7 +2894,7 @@
         <v>-0.0623</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4698</v>
+        <v>-0.4916</v>
       </c>
       <c r="E54" t="n">
         <v>-0.1198</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.2169</v>
+        <v>-0.2139</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.1129</v>
+        <v>-0.1113</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.509</v>
+        <v>-0.5291</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.2169</v>
+        <v>-0.2139</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.4016</v>
+        <v>-0.3986</v>
       </c>
       <c r="G55" t="n">
         <v>0.1847</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.4016</v>
+        <v>-0.3986</v>
       </c>
       <c r="I55" t="n">
         <v>-0.4053</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1207</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.515</v>
+        <v>-0.5363</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2319</v>
@@ -3032,7 +3032,7 @@
         <v>-0.1307</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5228</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2511</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2092</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5838</v>
+        <v>-0.6041</v>
       </c>
       <c r="E58" t="n">
         <v>-0.4021</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4317</v>
+        <v>-0.4294</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2246</v>
+        <v>-0.2234</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5958</v>
+        <v>-0.615</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4317</v>
+        <v>-0.4294</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.3072</v>
+        <v>-0.3049</v>
       </c>
       <c r="G59" t="n">
         <v>-0.1245</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3072</v>
+        <v>-0.3049</v>
       </c>
       <c r="I59" t="n">
         <v>-0.3101</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2344</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6034</v>
+        <v>-0.6234</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4505</v>
@@ -3216,7 +3216,7 @@
         <v>-0.2402</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6079</v>
+        <v>-0.6279</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4617</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2495</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6151</v>
+        <v>-0.635</v>
       </c>
       <c r="E62" t="n">
         <v>-0.4796</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2523</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6172</v>
+        <v>-0.6371</v>
       </c>
       <c r="E63" t="n">
         <v>-0.4848</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2709</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6317</v>
+        <v>-0.6513</v>
       </c>
       <c r="E64" t="n">
         <v>-0.5206</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5838</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3061</v>
+        <v>-0.3038</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.659</v>
+        <v>-0.6765</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5838</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5838</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.5838</v>
       </c>
       <c r="I65" t="n">
         <v>-0.5937</v>
@@ -3446,7 +3446,7 @@
         <v>-0.3252</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6738</v>
+        <v>-0.6929</v>
       </c>
       <c r="E66" t="n">
         <v>-0.625</v>
@@ -3492,7 +3492,7 @@
         <v>-0.3427</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6874</v>
+        <v>-0.7063</v>
       </c>
       <c r="E67" t="n">
         <v>-0.6586</v>
@@ -3538,7 +3538,7 @@
         <v>-0.487</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7995</v>
+        <v>-0.8168</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9360000000000001</v>
@@ -3584,7 +3584,7 @@
         <v>-0.4991</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8089</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9593</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.9785</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.509</v>
+        <v>-0.5091</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8166</v>
+        <v>-0.8337</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.9785</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0217</v>
+        <v>0.0215</v>
       </c>
       <c r="G70" t="n">
         <v>-1</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0217</v>
+        <v>0.0215</v>
       </c>
       <c r="I70" t="n">
         <v>0.0219</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5358000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8373</v>
+        <v>-0.8541</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0297</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5425</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8425</v>
+        <v>-0.8593</v>
       </c>
       <c r="E72" t="n">
         <v>-1.0426</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5714</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.865</v>
+        <v>-0.8814</v>
       </c>
       <c r="E73" t="n">
         <v>-1.0982</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8433</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0761</v>
+        <v>-1.0896</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6208</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9579</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1651</v>
+        <v>-1.1774</v>
       </c>
       <c r="E75" t="n">
         <v>-1.841</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0406</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E76" t="n">
         <v>-2</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.7218</v>
+        <v>-2.704</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.4162</v>
+        <v>-1.4069</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5209</v>
+        <v>-1.5212</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.7218</v>
+        <v>-2.704</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.3922</v>
+        <v>-2.3744</v>
       </c>
       <c r="G77" t="n">
         <v>-0.3296</v>
       </c>
       <c r="H77" t="n">
-        <v>-2.3922</v>
+        <v>-2.3744</v>
       </c>
       <c r="I77" t="n">
         <v>-2.4145</v>
@@ -3998,7 +3998,7 @@
         <v>-1.5898</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.6557</v>
+        <v>-1.6612</v>
       </c>
       <c r="E78" t="n">
         <v>-3.0555</v>
@@ -4044,7 +4044,7 @@
         <v>-1.7508</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7807</v>
+        <v>-1.7844</v>
       </c>
       <c r="E79" t="n">
         <v>-3.3648</v>
@@ -4090,7 +4090,7 @@
         <v>-2.275</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.1877</v>
+        <v>-2.1859</v>
       </c>
       <c r="E80" t="n">
         <v>-4.3724</v>
@@ -4136,7 +4136,7 @@
         <v>-2.2975</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2051</v>
+        <v>-2.203</v>
       </c>
       <c r="E81" t="n">
         <v>-4.4155</v>

--- a/database/event/8036/event_8036_evp_summary.xlsx
+++ b/database/event/8036/event_8036_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.4383</v>
+        <v>10.5781</v>
       </c>
       <c r="C2" t="n">
-        <v>5.4313</v>
+        <v>5.504</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1275</v>
+        <v>4.1112</v>
       </c>
       <c r="E2" t="n">
-        <v>10.4383</v>
+        <v>10.5781</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5155</v>
+        <v>3.5158</v>
       </c>
       <c r="G2" t="n">
-        <v>6.9227</v>
+        <v>6.9221</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7049</v>
+        <v>6.7057</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6206</v>
+        <v>3.621</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9227</v>
+        <v>6.9221</v>
       </c>
       <c r="K2" t="n">
         <v>125</v>
@@ -529,7 +529,7 @@
         <v>162</v>
       </c>
       <c r="M2" t="n">
-        <v>10.5433</v>
+        <v>10.5431</v>
       </c>
       <c r="N2" t="n">
         <v>287</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.3103</v>
+        <v>9.5144</v>
       </c>
       <c r="C3" t="n">
-        <v>4.8443</v>
+        <v>4.9505</v>
       </c>
       <c r="D3" t="n">
-        <v>3.614</v>
+        <v>3.6361</v>
       </c>
       <c r="E3" t="n">
-        <v>9.3103</v>
+        <v>9.5144</v>
       </c>
       <c r="F3" t="n">
         <v>4.5807</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7296</v>
+        <v>4.7448</v>
       </c>
       <c r="H3" t="n">
-        <v>10.5789</v>
+        <v>10.6166</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7125</v>
+        <v>5.7329</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7296</v>
+        <v>4.7448</v>
       </c>
       <c r="K3" t="n">
         <v>125</v>
@@ -575,7 +575,7 @@
         <v>162</v>
       </c>
       <c r="M3" t="n">
-        <v>10.4421</v>
+        <v>10.4777</v>
       </c>
       <c r="N3" t="n">
         <v>287</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.2065</v>
+        <v>8.41</v>
       </c>
       <c r="C4" t="n">
-        <v>4.27</v>
+        <v>4.3759</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1116</v>
+        <v>3.1427</v>
       </c>
       <c r="E4" t="n">
-        <v>8.2065</v>
+        <v>8.41</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0369</v>
+        <v>3.0371</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1696</v>
+        <v>5.1695</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9219</v>
+        <v>3.9224</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9219</v>
+        <v>3.9224</v>
       </c>
       <c r="J4" t="n">
-        <v>5.1696</v>
+        <v>5.1695</v>
       </c>
       <c r="K4" t="n">
         <v>156</v>
@@ -621,7 +621,7 @@
         <v>198</v>
       </c>
       <c r="M4" t="n">
-        <v>9.0915</v>
+        <v>9.091900000000001</v>
       </c>
       <c r="N4" t="n">
         <v>354</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.4652</v>
+        <v>6.568</v>
       </c>
       <c r="C5" t="n">
-        <v>3.364</v>
+        <v>3.4175</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3189</v>
+        <v>2.32</v>
       </c>
       <c r="E5" t="n">
-        <v>6.4652</v>
+        <v>6.568</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1529</v>
+        <v>3.153</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3123</v>
+        <v>3.3348</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1758</v>
+        <v>4.1761</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1758</v>
+        <v>4.1761</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3123</v>
+        <v>3.3348</v>
       </c>
       <c r="K5" t="n">
         <v>156</v>
@@ -667,7 +667,7 @@
         <v>198</v>
       </c>
       <c r="M5" t="n">
-        <v>7.488099999999999</v>
+        <v>7.510899999999999</v>
       </c>
       <c r="N5" t="n">
         <v>354</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.0867</v>
+        <v>6.1753</v>
       </c>
       <c r="C6" t="n">
-        <v>3.167</v>
+        <v>3.2131</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1466</v>
+        <v>2.1446</v>
       </c>
       <c r="E6" t="n">
-        <v>6.0867</v>
+        <v>6.1753</v>
       </c>
       <c r="F6" t="n">
         <v>4.5807</v>
       </c>
       <c r="G6" t="n">
-        <v>1.506</v>
+        <v>1.5056</v>
       </c>
       <c r="H6" t="n">
-        <v>10.3326</v>
+        <v>10.294</v>
       </c>
       <c r="I6" t="n">
-        <v>5.5795</v>
+        <v>5.5587</v>
       </c>
       <c r="J6" t="n">
-        <v>1.506</v>
+        <v>1.5056</v>
       </c>
       <c r="K6" t="n">
         <v>125</v>
@@ -713,7 +713,7 @@
         <v>162</v>
       </c>
       <c r="M6" t="n">
-        <v>7.085500000000001</v>
+        <v>7.0643</v>
       </c>
       <c r="N6" t="n">
         <v>287</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.6308</v>
+        <v>5.6382</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9298</v>
+        <v>2.9337</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9391</v>
+        <v>1.9046</v>
       </c>
       <c r="E7" t="n">
-        <v>5.6308</v>
+        <v>5.6382</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1735</v>
+        <v>1.1526</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4573</v>
+        <v>4.4571</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1735</v>
+        <v>1.1526</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1735</v>
+        <v>1.1526</v>
       </c>
       <c r="J7" t="n">
-        <v>4.4573</v>
+        <v>4.4571</v>
       </c>
       <c r="K7" t="n">
         <v>156</v>
@@ -759,7 +759,7 @@
         <v>198</v>
       </c>
       <c r="M7" t="n">
-        <v>5.6308</v>
+        <v>5.6097</v>
       </c>
       <c r="N7" t="n">
         <v>354</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.6112</v>
+        <v>5.5962</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9196</v>
+        <v>2.9118</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9301</v>
+        <v>1.8859</v>
       </c>
       <c r="E8" t="n">
-        <v>5.6112</v>
+        <v>5.5962</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1512</v>
+        <v>3.1371</v>
       </c>
       <c r="G8" t="n">
-        <v>2.46</v>
+        <v>2.4714</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5029</v>
+        <v>5.4564</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9715</v>
+        <v>2.9464</v>
       </c>
       <c r="J8" t="n">
-        <v>2.46</v>
+        <v>2.4714</v>
       </c>
       <c r="K8" t="n">
         <v>125</v>
@@ -805,7 +805,7 @@
         <v>162</v>
       </c>
       <c r="M8" t="n">
-        <v>5.4315</v>
+        <v>5.4178</v>
       </c>
       <c r="N8" t="n">
         <v>287</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.1124</v>
+        <v>5.1298</v>
       </c>
       <c r="C9" t="n">
-        <v>2.6601</v>
+        <v>2.6691</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7031</v>
+        <v>1.6775</v>
       </c>
       <c r="E9" t="n">
-        <v>5.1124</v>
+        <v>5.1298</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7532</v>
+        <v>1.7537</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3592</v>
+        <v>3.3589</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7532</v>
+        <v>1.7537</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7532</v>
+        <v>1.7537</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3592</v>
+        <v>3.3589</v>
       </c>
       <c r="K9" t="n">
         <v>156</v>
@@ -851,7 +851,7 @@
         <v>198</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1124</v>
+        <v>5.1126</v>
       </c>
       <c r="N9" t="n">
         <v>354</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.553</v>
+        <v>4.5953</v>
       </c>
       <c r="C10" t="n">
-        <v>2.369</v>
+        <v>2.391</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4484</v>
+        <v>1.4388</v>
       </c>
       <c r="E10" t="n">
-        <v>4.553</v>
+        <v>4.5953</v>
       </c>
       <c r="F10" t="n">
-        <v>3.047</v>
+        <v>3.035</v>
       </c>
       <c r="G10" t="n">
-        <v>1.506</v>
+        <v>1.5247</v>
       </c>
       <c r="H10" t="n">
-        <v>3.944</v>
+        <v>3.9178</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1499</v>
+        <v>4.1223</v>
       </c>
       <c r="J10" t="n">
-        <v>1.506</v>
+        <v>1.5247</v>
       </c>
       <c r="K10" t="n">
         <v>209</v>
@@ -897,7 +897,7 @@
         <v>60</v>
       </c>
       <c r="M10" t="n">
-        <v>5.6559</v>
+        <v>5.647</v>
       </c>
       <c r="N10" t="n">
         <v>269</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0301</v>
+        <v>4.3222</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0969</v>
+        <v>2.2489</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2104</v>
+        <v>1.3168</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0301</v>
+        <v>4.3222</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0648</v>
+        <v>4.0646</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0347</v>
       </c>
       <c r="H11" t="n">
-        <v>8.517200000000001</v>
+        <v>8.516400000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5992</v>
+        <v>4.5988</v>
       </c>
       <c r="J11" t="n">
         <v>-0.0347</v>
@@ -943,7 +943,7 @@
         <v>35</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5645</v>
+        <v>4.5641</v>
       </c>
       <c r="N11" t="n">
         <v>187</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.8241</v>
+        <v>4.0431</v>
       </c>
       <c r="C12" t="n">
-        <v>1.9898</v>
+        <v>2.1037</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1166</v>
+        <v>1.1921</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8241</v>
+        <v>4.0431</v>
       </c>
       <c r="F12" t="n">
-        <v>4.5926</v>
+        <v>4.6014</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7685</v>
       </c>
       <c r="H12" t="n">
-        <v>7.3269</v>
+        <v>7.346</v>
       </c>
       <c r="I12" t="n">
-        <v>7.7094</v>
+        <v>7.7295</v>
       </c>
       <c r="J12" t="n">
         <v>-0.7685</v>
@@ -989,7 +989,7 @@
         <v>33</v>
       </c>
       <c r="M12" t="n">
-        <v>6.940899999999999</v>
+        <v>6.961</v>
       </c>
       <c r="N12" t="n">
         <v>235</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>regali</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.6827</v>
+        <v>4.0068</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9162</v>
+        <v>2.0848</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0522</v>
+        <v>1.1759</v>
       </c>
       <c r="E13" t="n">
-        <v>3.6827</v>
+        <v>4.0068</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2089</v>
+        <v>3.6156</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4738</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6932</v>
+        <v>5.1884</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0743</v>
+        <v>5.1884</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4738</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="L13" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5481</v>
+        <v>5.1884</v>
       </c>
       <c r="N13" t="n">
-        <v>187</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>regali</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.6157</v>
+        <v>3.7095</v>
       </c>
       <c r="C14" t="n">
-        <v>1.8813</v>
+        <v>1.9301</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0217</v>
+        <v>1.0431</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6157</v>
+        <v>3.7095</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6157</v>
+        <v>3.4357</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1887</v>
+        <v>4.7948</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1887</v>
+        <v>4.7948</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1887</v>
+        <v>4.7948</v>
       </c>
       <c r="N14" t="n">
-        <v>142</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.5648</v>
+        <v>3.6972</v>
       </c>
       <c r="C15" t="n">
-        <v>1.8548</v>
+        <v>1.9237</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9986</v>
+        <v>1.0376</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5648</v>
+        <v>3.6972</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7961</v>
+        <v>3.2306</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7687</v>
+        <v>0.4738</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3948</v>
+        <v>5.7649</v>
       </c>
       <c r="I15" t="n">
-        <v>3.572</v>
+        <v>3.113</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7687</v>
+        <v>0.4738</v>
       </c>
       <c r="K15" t="n">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3407</v>
+        <v>3.5868</v>
       </c>
       <c r="N15" t="n">
-        <v>269</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4357</v>
+        <v>3.6732</v>
       </c>
       <c r="C16" t="n">
-        <v>1.7877</v>
+        <v>1.9112</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9398</v>
+        <v>1.0269</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4357</v>
+        <v>3.6732</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4357</v>
+        <v>2.7647</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.7682</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7948</v>
+        <v>3.3262</v>
       </c>
       <c r="I16" t="n">
-        <v>4.7948</v>
+        <v>3.4998</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.7682</v>
       </c>
       <c r="K16" t="n">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M16" t="n">
-        <v>4.7948</v>
+        <v>4.268</v>
       </c>
       <c r="N16" t="n">
-        <v>167</v>
+        <v>269</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.2158</v>
+        <v>3.3278</v>
       </c>
       <c r="C17" t="n">
-        <v>1.6732</v>
+        <v>1.7315</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8397</v>
+        <v>0.8726</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2158</v>
+        <v>3.3278</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4608</v>
+        <v>3.4578</v>
       </c>
       <c r="G17" t="n">
         <v>-0.245</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8497</v>
+        <v>4.8432</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8497</v>
+        <v>4.8432</v>
       </c>
       <c r="J17" t="n">
         <v>-0.245</v>
@@ -1219,7 +1219,7 @@
         <v>92</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6047</v>
+        <v>4.5982</v>
       </c>
       <c r="N17" t="n">
         <v>260</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.1795</v>
+        <v>3.2924</v>
       </c>
       <c r="C18" t="n">
-        <v>1.6544</v>
+        <v>1.7131</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8232</v>
+        <v>0.8568</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1795</v>
+        <v>3.2924</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1795</v>
+        <v>3.174</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.234</v>
+        <v>4.222</v>
       </c>
       <c r="I18" t="n">
-        <v>4.455</v>
+        <v>4.4424</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.455</v>
+        <v>4.4424</v>
       </c>
       <c r="N18" t="n">
         <v>251</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.9582</v>
+        <v>3.0478</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5392</v>
+        <v>1.5858</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7224</v>
+        <v>0.7476</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9582</v>
+        <v>3.0478</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9582</v>
+        <v>3.7289</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.7917</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7496</v>
+        <v>5.4364</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9453</v>
+        <v>5.7202</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.7917</v>
       </c>
       <c r="K19" t="n">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9453</v>
+        <v>4.928500000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>251</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9374</v>
+        <v>2.9444</v>
       </c>
       <c r="C20" t="n">
-        <v>1.5284</v>
+        <v>1.532</v>
       </c>
       <c r="D20" t="n">
-        <v>0.713</v>
+        <v>0.7014</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9374</v>
+        <v>2.9444</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7291</v>
+        <v>2.9646</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7917</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.437</v>
+        <v>3.7637</v>
       </c>
       <c r="I20" t="n">
-        <v>5.7208</v>
+        <v>3.9602</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7917</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="L20" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.9291</v>
+        <v>3.9602</v>
       </c>
       <c r="N20" t="n">
-        <v>235</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7891</v>
+        <v>2.8801</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4512</v>
+        <v>1.4986</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6455</v>
+        <v>0.6727</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7891</v>
+        <v>2.8801</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7891</v>
+        <v>2.7888</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3795</v>
+        <v>3.3789</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3795</v>
+        <v>3.3789</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3795</v>
+        <v>3.3789</v>
       </c>
       <c r="N21" t="n">
         <v>191</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6227</v>
+        <v>2.6596</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3646</v>
+        <v>1.3838</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5697</v>
+        <v>0.5742</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6227</v>
+        <v>2.6596</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4696</v>
+        <v>2.4695</v>
       </c>
       <c r="G22" t="n">
         <v>0.1531</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2539</v>
+        <v>3.2536</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7571</v>
+        <v>1.7569</v>
       </c>
       <c r="J22" t="n">
         <v>0.1531</v>
@@ -1449,7 +1449,7 @@
         <v>35</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9102</v>
+        <v>1.91</v>
       </c>
       <c r="N22" t="n">
         <v>187</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.4966</v>
+        <v>2.496</v>
       </c>
       <c r="C23" t="n">
-        <v>1.299</v>
+        <v>1.2987</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5123</v>
+        <v>0.5011</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4966</v>
+        <v>2.496</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4966</v>
+        <v>2.396</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.7394</v>
+        <v>2.5192</v>
       </c>
       <c r="I23" t="n">
-        <v>2.7394</v>
+        <v>2.5192</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7394</v>
+        <v>2.5192</v>
       </c>
       <c r="N23" t="n">
         <v>191</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.3962</v>
+        <v>2.4144</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2468</v>
+        <v>1.2563</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4666</v>
+        <v>0.4646</v>
       </c>
       <c r="E24" t="n">
-        <v>2.3962</v>
+        <v>2.4144</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3962</v>
+        <v>2.5248</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5196</v>
+        <v>2.801</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5196</v>
+        <v>2.801</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5196</v>
+        <v>2.801</v>
       </c>
       <c r="N24" t="n">
         <v>191</v>
@@ -1554,16 +1554,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.3218</v>
+        <v>2.4027</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2081</v>
+        <v>1.2502</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4327</v>
+        <v>0.4594</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3218</v>
+        <v>2.4027</v>
       </c>
       <c r="F25" t="n">
         <v>2.3218</v>
@@ -1596,1381 +1596,1381 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.0456</v>
+        <v>2.2384</v>
       </c>
       <c r="C26" t="n">
-        <v>1.0644</v>
+        <v>1.1647</v>
       </c>
       <c r="D26" t="n">
-        <v>0.307</v>
+        <v>0.386</v>
       </c>
       <c r="E26" t="n">
-        <v>2.0456</v>
+        <v>2.2384</v>
       </c>
       <c r="F26" t="n">
-        <v>3.0456</v>
+        <v>1.7126</v>
       </c>
       <c r="G26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>5.1543</v>
+        <v>1.7126</v>
       </c>
       <c r="I26" t="n">
-        <v>2.7833</v>
+        <v>1.7126</v>
       </c>
       <c r="J26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7833</v>
+        <v>1.7126</v>
       </c>
       <c r="N26" t="n">
-        <v>187</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cxzi</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.9983</v>
+        <v>2.0253</v>
       </c>
       <c r="C27" t="n">
-        <v>1.0398</v>
+        <v>1.0538</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2855</v>
+        <v>0.2908</v>
       </c>
       <c r="E27" t="n">
-        <v>1.9983</v>
+        <v>2.0253</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9983</v>
+        <v>3.0346</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.9983</v>
+        <v>5.118</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9983</v>
+        <v>2.7637</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K27" t="n">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M27" t="n">
-        <v>1.9983</v>
+        <v>1.7637</v>
       </c>
       <c r="N27" t="n">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>Cxzi</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.8937</v>
+        <v>2.0164</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9853</v>
+        <v>1.0492</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2378</v>
+        <v>0.2869</v>
       </c>
       <c r="E28" t="n">
-        <v>1.8937</v>
+        <v>2.0164</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3106</v>
+        <v>1.9983</v>
       </c>
       <c r="G28" t="n">
-        <v>1.5831</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3106</v>
+        <v>1.9983</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3106</v>
+        <v>1.9983</v>
       </c>
       <c r="J28" t="n">
-        <v>1.5831</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L28" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.8937</v>
+        <v>1.9983</v>
       </c>
       <c r="N28" t="n">
-        <v>260</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.8859</v>
+        <v>2.0098</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9813</v>
+        <v>1.0457</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2343</v>
+        <v>0.2839</v>
       </c>
       <c r="E29" t="n">
-        <v>1.8859</v>
+        <v>2.0098</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3484</v>
+        <v>0.3111</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5375</v>
+        <v>1.5831</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3484</v>
+        <v>0.3111</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4188</v>
+        <v>0.3111</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5375</v>
+        <v>1.5831</v>
       </c>
       <c r="K29" t="n">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="M29" t="n">
-        <v>1.9563</v>
+        <v>1.8942</v>
       </c>
       <c r="N29" t="n">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.8098</v>
+        <v>1.9819</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9417</v>
+        <v>1.0312</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1997</v>
+        <v>0.2715</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8098</v>
+        <v>1.9819</v>
       </c>
       <c r="F30" t="n">
-        <v>1.8098</v>
+        <v>1.3494</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.5371</v>
       </c>
       <c r="H30" t="n">
-        <v>1.8098</v>
+        <v>1.3494</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8098</v>
+        <v>1.4198</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.5371</v>
       </c>
       <c r="K30" t="n">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M30" t="n">
-        <v>1.8098</v>
+        <v>1.9569</v>
       </c>
       <c r="N30" t="n">
-        <v>167</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.7975</v>
+        <v>1.8255</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9353</v>
+        <v>0.9498</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1941</v>
+        <v>0.2016</v>
       </c>
       <c r="E31" t="n">
-        <v>1.7975</v>
+        <v>1.8255</v>
       </c>
       <c r="F31" t="n">
-        <v>1.7975</v>
+        <v>1.797</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.7975</v>
+        <v>1.797</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8913</v>
+        <v>1.797</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>251</v>
+        <v>191</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.8913</v>
+        <v>1.797</v>
       </c>
       <c r="N31" t="n">
-        <v>251</v>
+        <v>191</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>cej0t</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.7972</v>
+        <v>1.7707</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9351</v>
+        <v>0.9213</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1939</v>
+        <v>0.1771</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7972</v>
+        <v>1.7707</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7972</v>
+        <v>1.3481</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7972</v>
+        <v>1.3481</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7972</v>
+        <v>1.3481</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.7972</v>
+        <v>1.3481</v>
       </c>
       <c r="N32" t="n">
-        <v>191</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.7128</v>
+        <v>1.7358</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8912</v>
+        <v>0.9032</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1555</v>
+        <v>0.1615</v>
       </c>
       <c r="E33" t="n">
-        <v>1.7128</v>
+        <v>1.7358</v>
       </c>
       <c r="F33" t="n">
-        <v>1.7128</v>
+        <v>1.8098</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7128</v>
+        <v>1.8098</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7128</v>
+        <v>1.8098</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.7128</v>
+        <v>1.8098</v>
       </c>
       <c r="N33" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.4909</v>
+        <v>1.6787</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0545</v>
+        <v>0.136</v>
       </c>
       <c r="E34" t="n">
-        <v>1.4909</v>
+        <v>1.6787</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4909</v>
+        <v>1.7966</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.4909</v>
+        <v>1.7966</v>
       </c>
       <c r="I34" t="n">
-        <v>1.4909</v>
+        <v>1.8904</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>191</v>
+        <v>251</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.4909</v>
+        <v>1.8904</v>
       </c>
       <c r="N34" t="n">
-        <v>191</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4193</v>
+        <v>1.5753</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7385</v>
+        <v>0.8197</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0219</v>
+        <v>0.0898</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4193</v>
+        <v>1.5753</v>
       </c>
       <c r="F35" t="n">
-        <v>1.4193</v>
+        <v>1.4902</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.4193</v>
+        <v>1.4902</v>
       </c>
       <c r="I35" t="n">
-        <v>1.4193</v>
+        <v>1.4902</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4193</v>
+        <v>1.4902</v>
       </c>
       <c r="N35" t="n">
-        <v>125</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.3642</v>
+        <v>1.482</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7098</v>
+        <v>0.7711</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0032</v>
+        <v>0.0482</v>
       </c>
       <c r="E36" t="n">
-        <v>1.3642</v>
+        <v>1.482</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3642</v>
+        <v>1.2302</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3642</v>
+        <v>1.2302</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4354</v>
+        <v>1.2302</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4354</v>
+        <v>1.2302</v>
       </c>
       <c r="N36" t="n">
-        <v>251</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cej0t</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.3481</v>
+        <v>1.4242</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7014</v>
+        <v>0.741</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0105</v>
+        <v>0.0223</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3481</v>
+        <v>1.4242</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3481</v>
+        <v>1.3637</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.3481</v>
+        <v>1.3637</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3481</v>
+        <v>1.4349</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>107</v>
+        <v>251</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.3481</v>
+        <v>1.4349</v>
       </c>
       <c r="N37" t="n">
-        <v>107</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3188</v>
+        <v>1.3133</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6862</v>
+        <v>0.6833</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0239</v>
+        <v>-0.0272</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3188</v>
+        <v>1.3133</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3188</v>
+        <v>1.4191</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3188</v>
+        <v>1.4191</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3188</v>
+        <v>1.4191</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3188</v>
+        <v>1.4191</v>
       </c>
       <c r="N38" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.2302</v>
+        <v>1.2546</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6401</v>
+        <v>0.6528</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0534</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2302</v>
+        <v>1.2546</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2302</v>
+        <v>1.1538</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.2302</v>
+        <v>1.1538</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2302</v>
+        <v>1.1538</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.2302</v>
+        <v>1.1538</v>
       </c>
       <c r="N39" t="n">
-        <v>82</v>
+        <v>168</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>hyped</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.1651</v>
+        <v>1.215</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6062</v>
+        <v>0.6322</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0711</v>
       </c>
       <c r="E40" t="n">
-        <v>1.1651</v>
+        <v>1.215</v>
       </c>
       <c r="F40" t="n">
-        <v>1.1651</v>
+        <v>0.9537</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1651</v>
+        <v>0.9537</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1651</v>
+        <v>0.9537</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.1651</v>
+        <v>0.9537</v>
       </c>
       <c r="N40" t="n">
-        <v>168</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.0487</v>
+        <v>1.185</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5457</v>
+        <v>0.6166</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1468</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>1.0487</v>
+        <v>1.185</v>
       </c>
       <c r="F41" t="n">
-        <v>1.0487</v>
+        <v>1.3312</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.0487</v>
+        <v>1.3312</v>
       </c>
       <c r="I41" t="n">
-        <v>1.0487</v>
+        <v>1.3312</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.0487</v>
+        <v>1.3312</v>
       </c>
       <c r="N41" t="n">
-        <v>108</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hyped</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9623</v>
+        <v>1.1232</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5007</v>
+        <v>0.5844</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1861</v>
+        <v>-0.1121</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9623</v>
+        <v>1.1232</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9623</v>
+        <v>1.0475</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9623</v>
+        <v>1.0475</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9623</v>
+        <v>1.0475</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9623</v>
+        <v>1.0475</v>
       </c>
       <c r="N42" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9322</v>
+        <v>1.1068</v>
       </c>
       <c r="C43" t="n">
-        <v>0.485</v>
+        <v>0.5759</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1998</v>
+        <v>-0.1194</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9322</v>
+        <v>1.1068</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9322</v>
+        <v>0.9277</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9322</v>
+        <v>0.9277</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9322</v>
+        <v>0.9277</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9322</v>
+        <v>0.9277</v>
       </c>
       <c r="N43" t="n">
-        <v>125</v>
+        <v>168</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Senzu</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9722</v>
       </c>
       <c r="C44" t="n">
-        <v>0.4828</v>
+        <v>0.5059</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2018</v>
+        <v>-0.1796</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9722</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9278999999999999</v>
+        <v>1.3575</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.4895</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9278999999999999</v>
+        <v>1.3575</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9278999999999999</v>
+        <v>1.3575</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.4895</v>
       </c>
       <c r="K44" t="n">
         <v>168</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.8679999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>168</v>
+        <v>260</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senzu</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8864</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4612</v>
+        <v>0.5038</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2207</v>
+        <v>-0.1813</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8864</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3759</v>
+        <v>0.7934</v>
       </c>
       <c r="G45" t="n">
-        <v>-0.4895</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.3759</v>
+        <v>0.7934</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3759</v>
+        <v>0.7934</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.4895</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="L45" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8863999999999999</v>
+        <v>0.7934</v>
       </c>
       <c r="N45" t="n">
-        <v>260</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7938</v>
+        <v>0.9648</v>
       </c>
       <c r="C46" t="n">
-        <v>0.413</v>
+        <v>0.502</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2628</v>
+        <v>-0.1829</v>
       </c>
       <c r="E46" t="n">
-        <v>0.7938</v>
+        <v>0.9648</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7938</v>
+        <v>0.9314</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.7938</v>
+        <v>0.9314</v>
       </c>
       <c r="I46" t="n">
-        <v>0.7938</v>
+        <v>0.9314</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7938</v>
+        <v>0.9314</v>
       </c>
       <c r="N46" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Ag1l</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7544</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3925</v>
+        <v>0.4188</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2808</v>
+        <v>-0.2543</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7544</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>1.5387</v>
+        <v>0.6412</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.7843</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.5387</v>
+        <v>0.6412</v>
       </c>
       <c r="I47" t="n">
-        <v>1.619</v>
+        <v>0.6412</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.7843</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="L47" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8347</v>
+        <v>0.6412</v>
       </c>
       <c r="N47" t="n">
-        <v>235</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ag1l</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6412</v>
+        <v>0.7145</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3336</v>
+        <v>0.3718</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3323</v>
+        <v>-0.2947</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6412</v>
+        <v>0.7145</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6412</v>
+        <v>1.5385</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.7843</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6412</v>
+        <v>1.5385</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6412</v>
+        <v>1.6188</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.7843</v>
       </c>
       <c r="K48" t="n">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6412</v>
+        <v>0.8345</v>
       </c>
       <c r="N48" t="n">
-        <v>107</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.629</v>
+        <v>0.617</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3273</v>
+        <v>0.321</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3379</v>
+        <v>-0.3382</v>
       </c>
       <c r="E49" t="n">
-        <v>0.629</v>
+        <v>0.617</v>
       </c>
       <c r="F49" t="n">
-        <v>0.629</v>
+        <v>0.3639</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.629</v>
+        <v>0.3639</v>
       </c>
       <c r="I49" t="n">
-        <v>0.629</v>
+        <v>0.3639</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.629</v>
+        <v>0.3639</v>
       </c>
       <c r="N49" t="n">
-        <v>167</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4654</v>
+        <v>0.4629</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2422</v>
+        <v>0.2409</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4123</v>
+        <v>-0.4071</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4654</v>
+        <v>0.4629</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4654</v>
+        <v>0.629</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4654</v>
+        <v>0.629</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4897</v>
+        <v>0.629</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>251</v>
+        <v>167</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.4897</v>
+        <v>0.629</v>
       </c>
       <c r="N50" t="n">
-        <v>251</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>FL4MUS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.3677</v>
+        <v>0.4333</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1913</v>
+        <v>0.2255</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4568</v>
+        <v>-0.4203</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3677</v>
+        <v>0.4333</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1851</v>
+        <v>0.3231</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1826</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1851</v>
+        <v>0.3231</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1948</v>
+        <v>0.3231</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1826</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="L51" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.3774</v>
+        <v>0.3231</v>
       </c>
       <c r="N51" t="n">
-        <v>235</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3639</v>
+        <v>0.3132</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1893</v>
+        <v>0.163</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4585</v>
+        <v>-0.4739</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3639</v>
+        <v>0.3132</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3639</v>
+        <v>0.7145</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.3517</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3639</v>
+        <v>0.7145</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3639</v>
+        <v>0.3858</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.3517</v>
       </c>
       <c r="K52" t="n">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3639</v>
+        <v>0.03409999999999996</v>
       </c>
       <c r="N52" t="n">
-        <v>82</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3633</v>
+        <v>0.2974</v>
       </c>
       <c r="C53" t="n">
-        <v>0.189</v>
+        <v>0.1547</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4588</v>
+        <v>-0.481</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3633</v>
+        <v>0.2974</v>
       </c>
       <c r="F53" t="n">
-        <v>0.715</v>
+        <v>0.1849</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.3517</v>
+        <v>0.1826</v>
       </c>
       <c r="H53" t="n">
-        <v>0.715</v>
+        <v>0.1849</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3861</v>
+        <v>0.1946</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.3517</v>
+        <v>0.1826</v>
       </c>
       <c r="K53" t="n">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="L53" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M53" t="n">
-        <v>0.03439999999999999</v>
+        <v>0.3772</v>
       </c>
       <c r="N53" t="n">
-        <v>187</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FL4MUS</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3147</v>
+        <v>0.2618</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1637</v>
+        <v>0.1362</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4809</v>
+        <v>-0.4969</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3147</v>
+        <v>0.2618</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3147</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3147</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3147</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>108</v>
+        <v>251</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3147</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>108</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>nettik</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2672</v>
+        <v>0.2166</v>
       </c>
       <c r="C55" t="n">
-        <v>0.139</v>
+        <v>0.1127</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5026</v>
+        <v>-0.5171</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2672</v>
+        <v>0.2166</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2672</v>
+        <v>0.1581</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2672</v>
+        <v>0.1581</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2672</v>
+        <v>0.1581</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2672</v>
+        <v>0.1581</v>
       </c>
       <c r="N55" t="n">
-        <v>168</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56">
@@ -2980,31 +2980,31 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2578</v>
+        <v>0.1777</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1341</v>
+        <v>0.0925</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5068</v>
+        <v>-0.5344</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2578</v>
+        <v>0.1777</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2187</v>
+        <v>0.2197</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0391</v>
+        <v>0.0388</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2187</v>
+        <v>0.2197</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2301</v>
+        <v>0.2312</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0391</v>
+        <v>0.0388</v>
       </c>
       <c r="K56" t="n">
         <v>209</v>
@@ -3013,7 +3013,7 @@
         <v>60</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2692</v>
+        <v>0.27</v>
       </c>
       <c r="N56" t="n">
         <v>269</v>
@@ -3022,139 +3022,139 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2461</v>
+        <v>0.1658</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1281</v>
+        <v>0.0863</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5122</v>
+        <v>-0.5397999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2461</v>
+        <v>0.1658</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2461</v>
+        <v>0.2832</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2461</v>
+        <v>0.2832</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2461</v>
+        <v>0.2832</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2461</v>
+        <v>0.2832</v>
       </c>
       <c r="N57" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.1935</v>
+        <v>0.1403</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1007</v>
+        <v>0.073</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5361</v>
+        <v>-0.5512</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1935</v>
+        <v>0.1403</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1935</v>
+        <v>0.2459</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1935</v>
+        <v>0.2459</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1935</v>
+        <v>0.2459</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1935</v>
+        <v>0.2459</v>
       </c>
       <c r="N58" t="n">
-        <v>115</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>nettik</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1583</v>
+        <v>0.0876</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0824</v>
+        <v>0.0456</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5521</v>
+        <v>-0.5747</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1583</v>
+        <v>0.0876</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1583</v>
+        <v>1.1468</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-1.1252</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1583</v>
+        <v>1.1468</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1583</v>
+        <v>1.1468</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-1.1252</v>
       </c>
       <c r="K59" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1583</v>
+        <v>0.02160000000000006</v>
       </c>
       <c r="N59" t="n">
-        <v>142</v>
+        <v>260</v>
       </c>
     </row>
     <row r="60">
@@ -3164,31 +3164,31 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.1363</v>
+        <v>0.0829</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0709</v>
+        <v>0.0431</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5622</v>
+        <v>-0.5768</v>
       </c>
       <c r="E60" t="n">
-        <v>0.1363</v>
+        <v>0.0829</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.0352</v>
+        <v>-1.0348</v>
       </c>
       <c r="G60" t="n">
-        <v>1.1715</v>
+        <v>1.1711</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.0352</v>
+        <v>-1.0348</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5588</v>
       </c>
       <c r="J60" t="n">
-        <v>1.1715</v>
+        <v>1.1711</v>
       </c>
       <c r="K60" t="n">
         <v>125</v>
@@ -3197,7 +3197,7 @@
         <v>162</v>
       </c>
       <c r="M60" t="n">
-        <v>0.6124999999999999</v>
+        <v>0.6123000000000001</v>
       </c>
       <c r="N60" t="n">
         <v>287</v>
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1346</v>
+        <v>0.0485</v>
       </c>
       <c r="C61" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0252</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5629</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1346</v>
+        <v>0.0485</v>
       </c>
       <c r="F61" t="n">
         <v>0.1346</v>
@@ -3252,369 +3252,369 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kyuubii</t>
+          <t>deemO</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0587</v>
+        <v>0.007</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0305</v>
+        <v>0.0036</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5975</v>
+        <v>-0.6107</v>
       </c>
       <c r="E62" t="n">
-        <v>0.0587</v>
+        <v>0.007</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0587</v>
+        <v>-0.089</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0587</v>
+        <v>-0.089</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0587</v>
+        <v>-0.089</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.0587</v>
+        <v>-0.089</v>
       </c>
       <c r="N62" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>kyuubii</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0209</v>
+        <v>-0.0184</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0109</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6147</v>
+        <v>-0.622</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0209</v>
+        <v>-0.0184</v>
       </c>
       <c r="F63" t="n">
-        <v>1.1461</v>
+        <v>0.0591</v>
       </c>
       <c r="G63" t="n">
-        <v>-1.1252</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.1461</v>
+        <v>0.0591</v>
       </c>
       <c r="I63" t="n">
-        <v>1.1461</v>
+        <v>0.0591</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.1252</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="L63" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.02089999999999992</v>
+        <v>0.0591</v>
       </c>
       <c r="N63" t="n">
-        <v>260</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>deemO</t>
+          <t>Krimbo</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.089</v>
+        <v>-0.0204</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0463</v>
+        <v>-0.0106</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6647</v>
+        <v>-0.6229</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.089</v>
+        <v>-0.0204</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.089</v>
+        <v>-0.1243</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.089</v>
+        <v>-0.1243</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.089</v>
+        <v>-0.1243</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.089</v>
+        <v>-0.1243</v>
       </c>
       <c r="N64" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1068</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0475</v>
+        <v>-0.0556</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6615</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1068</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1843</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1843</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1843</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.1843</v>
       </c>
       <c r="N65" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Krimbo</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.1245</v>
+        <v>-0.139</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0648</v>
+        <v>-0.0723</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1245</v>
+        <v>-0.139</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1245</v>
+        <v>-0.0727</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1245</v>
+        <v>-0.0727</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1245</v>
+        <v>-0.0727</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.1245</v>
+        <v>-0.0727</v>
       </c>
       <c r="N66" t="n">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.1352</v>
+        <v>-0.3509</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0703</v>
+        <v>-0.1826</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.6857</v>
+        <v>-0.7706</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.1352</v>
+        <v>-0.3509</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.1352</v>
+        <v>0.5879</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>-0.7498</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.1352</v>
+        <v>0.5879</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.1352</v>
+        <v>0.6186</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>-0.7498</v>
       </c>
       <c r="K67" t="n">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.1352</v>
+        <v>-0.1312</v>
       </c>
       <c r="N67" t="n">
-        <v>108</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.1627</v>
+        <v>-0.5255</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.0847</v>
+        <v>-0.2734</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.6983</v>
+        <v>-0.8485</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.1627</v>
+        <v>-0.5255</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5868</v>
+        <v>-0.4677</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5868</v>
+        <v>-0.4677</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6173999999999999</v>
+        <v>-0.4677</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="L68" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.1321000000000001</v>
+        <v>-0.4677</v>
       </c>
       <c r="N68" t="n">
-        <v>269</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4811</v>
+        <v>-0.5268</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2503</v>
+        <v>-0.2741</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.8491</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4811</v>
+        <v>-0.5268</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4811</v>
+        <v>-0.1203</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4811</v>
+        <v>-0.1203</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4811</v>
+        <v>-0.1203</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4811</v>
+        <v>-0.1203</v>
       </c>
       <c r="N69" t="n">
-        <v>168</v>
+        <v>108</v>
       </c>
     </row>
     <row r="70">
@@ -3624,28 +3624,28 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.5808</v>
+        <v>-0.7869</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3022</v>
+        <v>-0.4094</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8885999999999999</v>
+        <v>-0.9653</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5808</v>
+        <v>-0.7869</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.5808</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5808</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5808</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3657,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.5808</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="N70" t="n">
         <v>108</v>
@@ -3666,32 +3666,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MUTiRiS</t>
+          <t>story</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6603</v>
+        <v>-0.9044</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.3436</v>
+        <v>-0.4706</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9248</v>
+        <v>-1.0178</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6603</v>
+        <v>-0.9044</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6603</v>
+        <v>-0.7416</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6603</v>
+        <v>-0.7416</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6603</v>
+        <v>-0.7416</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6603</v>
+        <v>-0.7416</v>
       </c>
       <c r="N71" t="n">
         <v>107</v>
@@ -3712,32 +3712,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>story</t>
+          <t>MUTiRiS</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.7416</v>
+        <v>-1.0641</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.3859</v>
+        <v>-0.5537</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9618</v>
+        <v>-1.0891</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.7416</v>
+        <v>-1.0641</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.7416</v>
+        <v>-0.6603</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.7416</v>
+        <v>-0.6603</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.7416</v>
+        <v>-0.6603</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.7416</v>
+        <v>-0.6603</v>
       </c>
       <c r="N72" t="n">
         <v>107</v>
@@ -3758,93 +3758,93 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>JDC</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9228</v>
+        <v>-1.2022</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4802</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0443</v>
+        <v>-1.1508</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9228</v>
+        <v>-1.2022</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.9228</v>
+        <v>-1.0813</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.9228</v>
+        <v>-1.0813</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.9228</v>
+        <v>-1.0813</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.9228</v>
+        <v>-1.0813</v>
       </c>
       <c r="N73" t="n">
-        <v>82</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JDC</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0816</v>
+        <v>-1.2773</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5628</v>
+        <v>-0.6646</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1166</v>
+        <v>-1.1844</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0816</v>
+        <v>-1.2773</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0816</v>
+        <v>-0.9228</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0816</v>
+        <v>-0.9228</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.0816</v>
+        <v>-0.9228</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0816</v>
+        <v>-0.9228</v>
       </c>
       <c r="N74" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.358</v>
+        <v>-1.5526</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7066</v>
+        <v>-0.8078</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2424</v>
+        <v>-1.3073</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.358</v>
+        <v>-1.5526</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.358</v>
+        <v>-1.3583</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.358</v>
+        <v>-1.3583</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.358</v>
+        <v>-1.3583</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.358</v>
+        <v>-1.3583</v>
       </c>
       <c r="N75" t="n">
         <v>168</v>
@@ -3896,93 +3896,93 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>rikz</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.8835</v>
+        <v>-2.0838</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.98</v>
+        <v>-1.0842</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4816</v>
+        <v>-1.5446</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.8835</v>
+        <v>-2.0838</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8835</v>
+        <v>-1.631</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-0.3033</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.8835</v>
+        <v>-1.631</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.8835</v>
+        <v>-1.7161</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-0.3033</v>
       </c>
       <c r="K76" t="n">
-        <v>82</v>
+        <v>202</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.8835</v>
+        <v>-2.0194</v>
       </c>
       <c r="N76" t="n">
-        <v>82</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>rikz</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.9341</v>
+        <v>-2.4049</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.0064</v>
+        <v>-1.2513</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.5046</v>
+        <v>-1.688</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.9341</v>
+        <v>-2.4049</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.6308</v>
+        <v>-1.8835</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.3033</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.6308</v>
+        <v>-1.8835</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.7159</v>
+        <v>-1.8835</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.3033</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="L77" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.0192</v>
+        <v>-1.8835</v>
       </c>
       <c r="N77" t="n">
-        <v>235</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78">
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.4901</v>
+        <v>-2.7493</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.2956</v>
+        <v>-1.4305</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.7577</v>
+        <v>-1.8419</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.4901</v>
+        <v>-2.7493</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.4901</v>
+        <v>-2.4903</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.4901</v>
+        <v>-2.4903</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.4901</v>
+        <v>-2.4903</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.4901</v>
+        <v>-2.4903</v>
       </c>
       <c r="N78" t="n">
         <v>125</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.707</v>
+        <v>-3.168</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.4085</v>
+        <v>-1.6484</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.8565</v>
+        <v>-2.0289</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.707</v>
+        <v>-3.168</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.707</v>
+        <v>-2.7072</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.707</v>
+        <v>-2.7072</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.707</v>
+        <v>-2.7072</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.707</v>
+        <v>-2.7072</v>
       </c>
       <c r="N79" t="n">
         <v>142</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.4359</v>
+        <v>-3.6859</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.7878</v>
+        <v>-1.9178</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.1883</v>
+        <v>-2.2602</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.4359</v>
+        <v>-3.6859</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.228</v>
+        <v>-2.2277</v>
       </c>
       <c r="G80" t="n">
         <v>-1.2079</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.228</v>
+        <v>-2.2277</v>
       </c>
       <c r="I80" t="n">
-        <v>-2.228</v>
+        <v>-2.2277</v>
       </c>
       <c r="J80" t="n">
         <v>-1.2079</v>
@@ -4117,7 +4117,7 @@
         <v>198</v>
       </c>
       <c r="M80" t="n">
-        <v>-3.4359</v>
+        <v>-3.4356</v>
       </c>
       <c r="N80" t="n">
         <v>354</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.6489</v>
+        <v>-4.0036</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.8986</v>
+        <v>-2.0832</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.2853</v>
+        <v>-2.4021</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.6489</v>
+        <v>-4.0036</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1705</v>
+        <v>-2.1795</v>
       </c>
       <c r="G81" t="n">
         <v>-1.4784</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1705</v>
+        <v>-2.1795</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.1705</v>
+        <v>-2.1795</v>
       </c>
       <c r="J81" t="n">
         <v>-1.4784</v>
@@ -4163,7 +4163,7 @@
         <v>92</v>
       </c>
       <c r="M81" t="n">
-        <v>-3.6489</v>
+        <v>-3.6579</v>
       </c>
       <c r="N81" t="n">
         <v>260</v>
@@ -4669,10 +4669,10 @@
         <v>1.43</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5561</v>
+        <v>0.5558</v>
       </c>
       <c r="J12" t="n">
-        <v>15.5708</v>
+        <v>15.5624</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.34</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4597</v>
+        <v>0.4595</v>
       </c>
       <c r="J13" t="n">
-        <v>12.8716</v>
+        <v>12.866</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>1.16</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2521</v>
+        <v>0.252</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0588</v>
+        <v>7.056</v>
       </c>
     </row>
     <row r="15">
@@ -4786,13 +4786,13 @@
         <v>28</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0165</v>
+        <v>0.039</v>
       </c>
       <c r="J15" t="n">
-        <v>0.462</v>
+        <v>1.092</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.95</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1003</v>
+        <v>-0.1004</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.8084</v>
+        <v>-2.8112</v>
       </c>
     </row>
     <row r="17">
@@ -5666,13 +5666,13 @@
         <v>23</v>
       </c>
       <c r="H37" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4675</v>
+        <v>0.4789</v>
       </c>
       <c r="J37" t="n">
-        <v>10.7525</v>
+        <v>11.0147</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.182</v>
+        <v>0.1814</v>
       </c>
       <c r="J38" t="n">
-        <v>4.186</v>
+        <v>4.1722</v>
       </c>
     </row>
     <row r="39">
@@ -5746,13 +5746,13 @@
         <v>23</v>
       </c>
       <c r="H39" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0583</v>
+        <v>-0.0431</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.3409</v>
+        <v>-0.9913</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.9</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1471</v>
+        <v>-0.1475</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.3833</v>
+        <v>-3.3925</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.75</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3011</v>
+        <v>-0.3015</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.9253</v>
+        <v>-6.9345</v>
       </c>
     </row>
     <row r="42">
@@ -8866,13 +8866,13 @@
         <v>23</v>
       </c>
       <c r="H117" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9518</v>
+        <v>0.9705</v>
       </c>
       <c r="J117" t="n">
-        <v>21.8914</v>
+        <v>22.3215</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2596</v>
+        <v>0.2591</v>
       </c>
       <c r="J118" t="n">
-        <v>5.9708</v>
+        <v>5.9593</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.95</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0926</v>
+        <v>-0.093</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.1298</v>
+        <v>-2.139</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.93</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1183</v>
+        <v>-0.1186</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.7209</v>
+        <v>-2.7278</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.73</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3268</v>
+        <v>-0.3271</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.5164</v>
+        <v>-7.5233</v>
       </c>
     </row>
     <row r="122">
@@ -11469,10 +11469,10 @@
         <v>1.52</v>
       </c>
       <c r="I182" t="n">
-        <v>1.1281</v>
+        <v>1.129</v>
       </c>
       <c r="J182" t="n">
-        <v>23.6901</v>
+        <v>23.709</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>1.26</v>
       </c>
       <c r="I183" t="n">
-        <v>0.6687</v>
+        <v>0.6693</v>
       </c>
       <c r="J183" t="n">
-        <v>14.0427</v>
+        <v>14.0553</v>
       </c>
     </row>
     <row r="184">
@@ -11546,13 +11546,13 @@
         <v>21</v>
       </c>
       <c r="H184" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6066</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>12.7386</v>
+        <v>12.3102</v>
       </c>
     </row>
     <row r="185">
@@ -11589,10 +11589,10 @@
         <v>1.19</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5221</v>
+        <v>0.5226</v>
       </c>
       <c r="J185" t="n">
-        <v>10.9641</v>
+        <v>10.9746</v>
       </c>
     </row>
     <row r="186">
@@ -11626,13 +11626,13 @@
         <v>21</v>
       </c>
       <c r="H186" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4351</v>
+        <v>-0.4598</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.1371</v>
+        <v>-9.655799999999999</v>
       </c>
     </row>
     <row r="187">
@@ -12269,10 +12269,10 @@
         <v>1.43</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7644</v>
+        <v>0.7639</v>
       </c>
       <c r="J202" t="n">
-        <v>18.3456</v>
+        <v>18.3336</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>1.36</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6621</v>
+        <v>0.6616</v>
       </c>
       <c r="J203" t="n">
-        <v>15.8904</v>
+        <v>15.8784</v>
       </c>
     </row>
     <row r="204">
@@ -12346,13 +12346,13 @@
         <v>24</v>
       </c>
       <c r="H204" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2932</v>
+        <v>0.3106</v>
       </c>
       <c r="J204" t="n">
-        <v>7.0368</v>
+        <v>7.4544</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2108</v>
+        <v>-0.211</v>
       </c>
       <c r="J205" t="n">
-        <v>-5.0592</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.77</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.291</v>
+        <v>-0.2911</v>
       </c>
       <c r="J206" t="n">
-        <v>-6.984</v>
+        <v>-6.9864</v>
       </c>
     </row>
     <row r="207">
@@ -12869,10 +12869,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5616</v>
       </c>
       <c r="J217" t="n">
-        <v>12.342</v>
+        <v>12.3552</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.13</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3182</v>
+        <v>0.3187</v>
       </c>
       <c r="J218" t="n">
-        <v>7.0004</v>
+        <v>7.0114</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>0.99</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.023</v>
+        <v>-0.0229</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.506</v>
+        <v>-0.5038</v>
       </c>
     </row>
     <row r="220">
@@ -12986,13 +12986,13 @@
         <v>22</v>
       </c>
       <c r="H220" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2972</v>
+        <v>-0.3065</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.5384</v>
+        <v>-6.743</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.66</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3805</v>
+        <v>-0.3803</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.371</v>
+        <v>-8.3666</v>
       </c>
     </row>
     <row r="222">
@@ -13269,10 +13269,10 @@
         <v>1.22</v>
       </c>
       <c r="I227" t="n">
-        <v>0.4952</v>
+        <v>0.4959</v>
       </c>
       <c r="J227" t="n">
-        <v>9.904</v>
+        <v>9.917999999999999</v>
       </c>
     </row>
     <row r="228">
@@ -13306,13 +13306,13 @@
         <v>20</v>
       </c>
       <c r="H228" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4952</v>
+        <v>0.4785</v>
       </c>
       <c r="J228" t="n">
-        <v>9.904</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="229">
@@ -13349,10 +13349,10 @@
         <v>0.84</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2031</v>
+        <v>-0.2029</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.062</v>
+        <v>-4.058</v>
       </c>
     </row>
     <row r="230">
@@ -13389,10 +13389,10 @@
         <v>0.63</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4021</v>
+        <v>-0.4019</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.042</v>
+        <v>-8.038</v>
       </c>
     </row>
     <row r="231">
@@ -13429,10 +13429,10 @@
         <v>0.61</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4199</v>
+        <v>-0.4197</v>
       </c>
       <c r="J231" t="n">
-        <v>-8.398</v>
+        <v>-8.394</v>
       </c>
     </row>
     <row r="232">
@@ -13669,10 +13669,10 @@
         <v>1.69</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3205</v>
+        <v>1.3197</v>
       </c>
       <c r="J237" t="n">
-        <v>26.41</v>
+        <v>26.394</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.63</v>
       </c>
       <c r="I238" t="n">
-        <v>1.2444</v>
+        <v>1.2438</v>
       </c>
       <c r="J238" t="n">
-        <v>24.888</v>
+        <v>24.876</v>
       </c>
     </row>
     <row r="239">
@@ -13746,13 +13746,13 @@
         <v>20</v>
       </c>
       <c r="H239" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I239" t="n">
-        <v>1.0037</v>
+        <v>1.0185</v>
       </c>
       <c r="J239" t="n">
-        <v>20.074</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="240">
@@ -13786,13 +13786,13 @@
         <v>20</v>
       </c>
       <c r="H240" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3348</v>
+        <v>0.359</v>
       </c>
       <c r="J240" t="n">
-        <v>6.696</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2948</v>
+        <v>-0.2954</v>
       </c>
       <c r="J241" t="n">
-        <v>-5.896</v>
+        <v>-5.908</v>
       </c>
     </row>
     <row r="242">
@@ -14669,10 +14669,10 @@
         <v>1.87</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5484</v>
+        <v>1.5489</v>
       </c>
       <c r="J262" t="n">
-        <v>29.4196</v>
+        <v>29.4291</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.66</v>
       </c>
       <c r="I263" t="n">
-        <v>1.287</v>
+        <v>1.2874</v>
       </c>
       <c r="J263" t="n">
-        <v>24.453</v>
+        <v>24.4606</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.24</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6126</v>
+        <v>0.6128</v>
       </c>
       <c r="J264" t="n">
-        <v>11.6394</v>
+        <v>11.6432</v>
       </c>
     </row>
     <row r="265">
@@ -14786,13 +14786,13 @@
         <v>19</v>
       </c>
       <c r="H265" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>0.0026</v>
+        <v>-0.0569</v>
       </c>
       <c r="J265" t="n">
-        <v>0.0494</v>
+        <v>-1.0811</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>0.93</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.3205</v>
+        <v>-0.3202</v>
       </c>
       <c r="J266" t="n">
-        <v>-6.0895</v>
+        <v>-6.0838</v>
       </c>
     </row>
     <row r="267">
@@ -14866,13 +14866,13 @@
         <v>19</v>
       </c>
       <c r="H267" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.0301</v>
+        <v>-0.0141</v>
       </c>
       <c r="J267" t="n">
-        <v>-0.5719</v>
+        <v>-0.2679</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.0737</v>
       </c>
       <c r="J268" t="n">
-        <v>-1.3946</v>
+        <v>-1.4003</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.72</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3053</v>
+        <v>-0.3055</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.8007</v>
+        <v>-5.8045</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.67</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3509</v>
+        <v>-0.3511</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.6671</v>
+        <v>-6.6709</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.52</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4842</v>
+        <v>-0.4845</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.1998</v>
+        <v>-9.205500000000001</v>
       </c>
     </row>
     <row r="272">
@@ -15066,13 +15066,13 @@
         <v>23</v>
       </c>
       <c r="H272" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I272" t="n">
-        <v>1.2628</v>
+        <v>1.2497</v>
       </c>
       <c r="J272" t="n">
-        <v>29.0444</v>
+        <v>28.7431</v>
       </c>
     </row>
     <row r="273">
@@ -15109,10 +15109,10 @@
         <v>1.32</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8132</v>
+        <v>0.8138</v>
       </c>
       <c r="J273" t="n">
-        <v>18.7036</v>
+        <v>18.7174</v>
       </c>
     </row>
     <row r="274">
@@ -15149,10 +15149,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0412</v>
+        <v>0.0415</v>
       </c>
       <c r="J274" t="n">
-        <v>0.9476</v>
+        <v>0.9545</v>
       </c>
     </row>
     <row r="275">
@@ -15189,10 +15189,10 @@
         <v>0.89</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3912</v>
+        <v>-0.3908</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.9976</v>
+        <v>-8.9884</v>
       </c>
     </row>
     <row r="276">
@@ -15229,10 +15229,10 @@
         <v>0.76</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7009</v>
+        <v>-0.7005</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.1207</v>
+        <v>-16.1115</v>
       </c>
     </row>
     <row r="277">
@@ -18106,13 +18106,13 @@
         <v>18</v>
       </c>
       <c r="H348" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.0752</v>
+        <v>-0.0616</v>
       </c>
       <c r="J348" t="n">
-        <v>-1.3536</v>
+        <v>-1.1088</v>
       </c>
     </row>
     <row r="349">
@@ -18146,13 +18146,13 @@
         <v>18</v>
       </c>
       <c r="H349" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.1597</v>
+        <v>-0.1707</v>
       </c>
       <c r="J349" t="n">
-        <v>-2.8746</v>
+        <v>-3.0726</v>
       </c>
     </row>
     <row r="350">
@@ -19269,10 +19269,10 @@
         <v>1.27</v>
       </c>
       <c r="I377" t="n">
-        <v>0.5319</v>
+        <v>0.5315</v>
       </c>
       <c r="J377" t="n">
-        <v>12.7656</v>
+        <v>12.756</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.26</v>
       </c>
       <c r="I378" t="n">
-        <v>0.5161</v>
+        <v>0.5157</v>
       </c>
       <c r="J378" t="n">
-        <v>12.3864</v>
+        <v>12.3768</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>1.01</v>
       </c>
       <c r="I379" t="n">
-        <v>0.0358</v>
+        <v>0.0356</v>
       </c>
       <c r="J379" t="n">
-        <v>0.8592</v>
+        <v>0.8544</v>
       </c>
     </row>
     <row r="380">
@@ -19386,13 +19386,13 @@
         <v>24</v>
       </c>
       <c r="H380" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.092</v>
+        <v>-0.0785</v>
       </c>
       <c r="J380" t="n">
-        <v>-2.208</v>
+        <v>-1.884</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.88</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.1757</v>
+        <v>-0.1759</v>
       </c>
       <c r="J381" t="n">
-        <v>-4.2168</v>
+        <v>-4.2216</v>
       </c>
     </row>
     <row r="382">
@@ -20269,10 +20269,10 @@
         <v>1.14</v>
       </c>
       <c r="I402" t="n">
-        <v>0.4008</v>
+        <v>0.3999</v>
       </c>
       <c r="J402" t="n">
-        <v>7.6152</v>
+        <v>7.5981</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>0.8</v>
       </c>
       <c r="I403" t="n">
-        <v>-0.2322</v>
+        <v>-0.2324</v>
       </c>
       <c r="J403" t="n">
-        <v>-4.4118</v>
+        <v>-4.4156</v>
       </c>
     </row>
     <row r="404">
@@ -20346,13 +20346,13 @@
         <v>19</v>
       </c>
       <c r="H404" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.3061</v>
+        <v>-0.2971</v>
       </c>
       <c r="J404" t="n">
-        <v>-5.8159</v>
+        <v>-5.6449</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>0.67</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.3518</v>
+        <v>-0.352</v>
       </c>
       <c r="J405" t="n">
-        <v>-6.6842</v>
+        <v>-6.688</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.53</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.4764</v>
+        <v>-0.4766</v>
       </c>
       <c r="J406" t="n">
-        <v>-9.051600000000001</v>
+        <v>-9.055400000000001</v>
       </c>
     </row>
     <row r="407">
@@ -22266,13 +22266,13 @@
         <v>21</v>
       </c>
       <c r="H452" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I452" t="n">
-        <v>0.0236</v>
+        <v>0.0678</v>
       </c>
       <c r="J452" t="n">
-        <v>0.4956</v>
+        <v>1.4238</v>
       </c>
     </row>
     <row r="453">
@@ -22309,10 +22309,10 @@
         <v>0.9</v>
       </c>
       <c r="I453" t="n">
-        <v>-0.1366</v>
+        <v>-0.1368</v>
       </c>
       <c r="J453" t="n">
-        <v>-2.8686</v>
+        <v>-2.8728</v>
       </c>
     </row>
     <row r="454">
@@ -22349,10 +22349,10 @@
         <v>0.85</v>
       </c>
       <c r="I454" t="n">
-        <v>-0.1895</v>
+        <v>-0.1896</v>
       </c>
       <c r="J454" t="n">
-        <v>-3.9795</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="455">
@@ -22389,10 +22389,10 @@
         <v>0.85</v>
       </c>
       <c r="I455" t="n">
-        <v>-0.1895</v>
+        <v>-0.1896</v>
       </c>
       <c r="J455" t="n">
-        <v>-3.9795</v>
+        <v>-3.9816</v>
       </c>
     </row>
     <row r="456">
@@ -22429,10 +22429,10 @@
         <v>0.71</v>
       </c>
       <c r="I456" t="n">
-        <v>-0.325</v>
+        <v>-0.3252</v>
       </c>
       <c r="J456" t="n">
-        <v>-6.825</v>
+        <v>-6.8292</v>
       </c>
     </row>
     <row r="457">
@@ -22469,10 +22469,10 @@
         <v>1.61</v>
       </c>
       <c r="I457" t="n">
-        <v>1.2393</v>
+        <v>1.2398</v>
       </c>
       <c r="J457" t="n">
-        <v>26.0253</v>
+        <v>26.0358</v>
       </c>
     </row>
     <row r="458">
@@ -22509,10 +22509,10 @@
         <v>1.48</v>
       </c>
       <c r="I458" t="n">
-        <v>1.0651</v>
+        <v>1.0655</v>
       </c>
       <c r="J458" t="n">
-        <v>22.3671</v>
+        <v>22.3755</v>
       </c>
     </row>
     <row r="459">
@@ -22546,13 +22546,13 @@
         <v>21</v>
       </c>
       <c r="H459" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="I459" t="n">
-        <v>0.8991</v>
+        <v>0.8803</v>
       </c>
       <c r="J459" t="n">
-        <v>18.8811</v>
+        <v>18.4863</v>
       </c>
     </row>
     <row r="460">
@@ -22589,10 +22589,10 @@
         <v>0.97</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.1815</v>
+        <v>-0.1812</v>
       </c>
       <c r="J460" t="n">
-        <v>-3.8115</v>
+        <v>-3.8052</v>
       </c>
     </row>
     <row r="461">
@@ -22629,10 +22629,10 @@
         <v>0.85</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.5169</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="J461" t="n">
-        <v>-10.8549</v>
+        <v>-10.8486</v>
       </c>
     </row>
     <row r="462">
@@ -23066,13 +23066,13 @@
         <v>19</v>
       </c>
       <c r="H472" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I472" t="n">
-        <v>0.2706</v>
+        <v>0.2907</v>
       </c>
       <c r="J472" t="n">
-        <v>5.1414</v>
+        <v>5.5233</v>
       </c>
     </row>
     <row r="473">
@@ -23109,10 +23109,10 @@
         <v>1.01</v>
       </c>
       <c r="I473" t="n">
-        <v>0.0726</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J473" t="n">
-        <v>1.3794</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="474">
@@ -23149,10 +23149,10 @@
         <v>0.74</v>
       </c>
       <c r="I474" t="n">
-        <v>-0.2953</v>
+        <v>-0.2955</v>
       </c>
       <c r="J474" t="n">
-        <v>-5.6107</v>
+        <v>-5.6145</v>
       </c>
     </row>
     <row r="475">
@@ -23189,10 +23189,10 @@
         <v>0.73</v>
       </c>
       <c r="I475" t="n">
-        <v>-0.3047</v>
+        <v>-0.3049</v>
       </c>
       <c r="J475" t="n">
-        <v>-5.7893</v>
+        <v>-5.7931</v>
       </c>
     </row>
     <row r="476">
@@ -23229,10 +23229,10 @@
         <v>0.66</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.3692</v>
+        <v>-0.3694</v>
       </c>
       <c r="J476" t="n">
-        <v>-7.0148</v>
+        <v>-7.0186</v>
       </c>
     </row>
     <row r="477">
@@ -23269,10 +23269,10 @@
         <v>1.97</v>
       </c>
       <c r="I477" t="n">
-        <v>1.677</v>
+        <v>1.6776</v>
       </c>
       <c r="J477" t="n">
-        <v>31.863</v>
+        <v>31.8744</v>
       </c>
     </row>
     <row r="478">
@@ -23306,13 +23306,13 @@
         <v>19</v>
       </c>
       <c r="H478" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I478" t="n">
-        <v>0.8139</v>
+        <v>0.7951</v>
       </c>
       <c r="J478" t="n">
-        <v>15.4641</v>
+        <v>15.1069</v>
       </c>
     </row>
     <row r="479">
@@ -23349,10 +23349,10 @@
         <v>1.21</v>
       </c>
       <c r="I479" t="n">
-        <v>0.5524</v>
+        <v>0.5527</v>
       </c>
       <c r="J479" t="n">
-        <v>10.4956</v>
+        <v>10.5013</v>
       </c>
     </row>
     <row r="480">
@@ -23389,10 +23389,10 @@
         <v>1.13</v>
       </c>
       <c r="I480" t="n">
-        <v>0.3678</v>
+        <v>0.3681</v>
       </c>
       <c r="J480" t="n">
-        <v>6.9882</v>
+        <v>6.9939</v>
       </c>
     </row>
     <row r="481">
@@ -23429,10 +23429,10 @@
         <v>0.92</v>
       </c>
       <c r="I481" t="n">
-        <v>-0.3445</v>
+        <v>-0.3442</v>
       </c>
       <c r="J481" t="n">
-        <v>-6.5455</v>
+        <v>-6.5398</v>
       </c>
     </row>
     <row r="482">
@@ -23669,10 +23669,10 @@
         <v>1.56</v>
       </c>
       <c r="I487" t="n">
-        <v>1.2029</v>
+        <v>1.2023</v>
       </c>
       <c r="J487" t="n">
-        <v>34.8841</v>
+        <v>34.8667</v>
       </c>
     </row>
     <row r="488">
@@ -23709,10 +23709,10 @@
         <v>1.36</v>
       </c>
       <c r="I488" t="n">
-        <v>0.8891</v>
+        <v>0.8885999999999999</v>
       </c>
       <c r="J488" t="n">
-        <v>25.7839</v>
+        <v>25.7694</v>
       </c>
     </row>
     <row r="489">
@@ -23749,10 +23749,10 @@
         <v>1.05</v>
       </c>
       <c r="I489" t="n">
-        <v>0.1807</v>
+        <v>0.1804</v>
       </c>
       <c r="J489" t="n">
-        <v>5.2403</v>
+        <v>5.2316</v>
       </c>
     </row>
     <row r="490">
@@ -23786,13 +23786,13 @@
         <v>29</v>
       </c>
       <c r="H490" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.4204</v>
+        <v>-0.3949</v>
       </c>
       <c r="J490" t="n">
-        <v>-12.1916</v>
+        <v>-11.4521</v>
       </c>
     </row>
     <row r="491">
@@ -23829,10 +23829,10 @@
         <v>0.82</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.5673</v>
+        <v>-0.5677</v>
       </c>
       <c r="J491" t="n">
-        <v>-16.4517</v>
+        <v>-16.4633</v>
       </c>
     </row>
     <row r="492">
@@ -25066,13 +25066,13 @@
         <v>18</v>
       </c>
       <c r="H522" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I522" t="n">
-        <v>1.4708</v>
+        <v>1.459</v>
       </c>
       <c r="J522" t="n">
-        <v>26.4744</v>
+        <v>26.262</v>
       </c>
     </row>
     <row r="523">
@@ -25109,10 +25109,10 @@
         <v>1.8</v>
       </c>
       <c r="I523" t="n">
-        <v>1.4585</v>
+        <v>1.459</v>
       </c>
       <c r="J523" t="n">
-        <v>26.253</v>
+        <v>26.262</v>
       </c>
     </row>
     <row r="524">
@@ -25149,10 +25149,10 @@
         <v>1.48</v>
       </c>
       <c r="I524" t="n">
-        <v>1.0489</v>
+        <v>1.0492</v>
       </c>
       <c r="J524" t="n">
-        <v>18.8802</v>
+        <v>18.8856</v>
       </c>
     </row>
     <row r="525">
@@ -25189,10 +25189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I525" t="n">
-        <v>-0.2939</v>
+        <v>-0.2936</v>
       </c>
       <c r="J525" t="n">
-        <v>-5.2902</v>
+        <v>-5.2848</v>
       </c>
     </row>
     <row r="526">
@@ -25229,10 +25229,10 @@
         <v>0.77</v>
       </c>
       <c r="I526" t="n">
-        <v>-0.717</v>
+        <v>-0.7167</v>
       </c>
       <c r="J526" t="n">
-        <v>-12.906</v>
+        <v>-12.9006</v>
       </c>
     </row>
     <row r="527">
@@ -26269,10 +26269,10 @@
         <v>1.46</v>
       </c>
       <c r="I552" t="n">
-        <v>1.0508</v>
+        <v>1.0513</v>
       </c>
       <c r="J552" t="n">
-        <v>23.1176</v>
+        <v>23.1286</v>
       </c>
     </row>
     <row r="553">
@@ -26309,10 +26309,10 @@
         <v>1.32</v>
       </c>
       <c r="I553" t="n">
-        <v>0.7961</v>
+        <v>0.7966</v>
       </c>
       <c r="J553" t="n">
-        <v>17.5142</v>
+        <v>17.5252</v>
       </c>
     </row>
     <row r="554">
@@ -26346,13 +26346,13 @@
         <v>22</v>
       </c>
       <c r="H554" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I554" t="n">
-        <v>0.6105</v>
+        <v>0.5896</v>
       </c>
       <c r="J554" t="n">
-        <v>13.431</v>
+        <v>12.9712</v>
       </c>
     </row>
     <row r="555">
@@ -26389,10 +26389,10 @@
         <v>1.08</v>
       </c>
       <c r="I555" t="n">
-        <v>0.259</v>
+        <v>0.2593</v>
       </c>
       <c r="J555" t="n">
-        <v>5.698</v>
+        <v>5.7046</v>
       </c>
     </row>
     <row r="556">
@@ -26429,10 +26429,10 @@
         <v>0.84</v>
       </c>
       <c r="I556" t="n">
-        <v>-0.529</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J556" t="n">
-        <v>-11.638</v>
+        <v>-11.6314</v>
       </c>
     </row>
     <row r="557">
@@ -26866,13 +26866,13 @@
         <v>15</v>
       </c>
       <c r="H567" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I567" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.0843</v>
       </c>
       <c r="J567" t="n">
-        <v>-1.4505</v>
+        <v>-1.2645</v>
       </c>
     </row>
     <row r="568">
@@ -26909,10 +26909,10 @@
         <v>0.84</v>
       </c>
       <c r="I568" t="n">
-        <v>-0.1887</v>
+        <v>-0.189</v>
       </c>
       <c r="J568" t="n">
-        <v>-2.8305</v>
+        <v>-2.835</v>
       </c>
     </row>
     <row r="569">
@@ -26949,10 +26949,10 @@
         <v>0.7</v>
       </c>
       <c r="I569" t="n">
-        <v>-0.3221</v>
+        <v>-0.3223</v>
       </c>
       <c r="J569" t="n">
-        <v>-4.8315</v>
+        <v>-4.8345</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>0.66</v>
       </c>
       <c r="I570" t="n">
-        <v>-0.3583</v>
+        <v>-0.3585</v>
       </c>
       <c r="J570" t="n">
-        <v>-5.3745</v>
+        <v>-5.3775</v>
       </c>
     </row>
     <row r="571">
@@ -27029,10 +27029,10 @@
         <v>0.63</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.3853</v>
+        <v>-0.3855</v>
       </c>
       <c r="J571" t="n">
-        <v>-5.7795</v>
+        <v>-5.7825</v>
       </c>
     </row>
     <row r="572">
@@ -27069,10 +27069,10 @@
         <v>1.42</v>
       </c>
       <c r="I572" t="n">
-        <v>0.9865</v>
+        <v>0.986</v>
       </c>
       <c r="J572" t="n">
-        <v>20.7165</v>
+        <v>20.706</v>
       </c>
     </row>
     <row r="573">
@@ -27109,10 +27109,10 @@
         <v>1.41</v>
       </c>
       <c r="I573" t="n">
-        <v>0.9691</v>
+        <v>0.9687</v>
       </c>
       <c r="J573" t="n">
-        <v>20.3511</v>
+        <v>20.3427</v>
       </c>
     </row>
     <row r="574">
@@ -27146,13 +27146,13 @@
         <v>21</v>
       </c>
       <c r="H574" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I574" t="n">
-        <v>0.7549</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="J574" t="n">
-        <v>15.8529</v>
+        <v>16.2687</v>
       </c>
     </row>
     <row r="575">
@@ -27189,10 +27189,10 @@
         <v>1.09</v>
       </c>
       <c r="I575" t="n">
-        <v>0.2855</v>
+        <v>0.2851</v>
       </c>
       <c r="J575" t="n">
-        <v>5.9955</v>
+        <v>5.9871</v>
       </c>
     </row>
     <row r="576">
@@ -27229,10 +27229,10 @@
         <v>0.73</v>
       </c>
       <c r="I576" t="n">
-        <v>-0.7793</v>
+        <v>-0.7796</v>
       </c>
       <c r="J576" t="n">
-        <v>-16.3653</v>
+        <v>-16.3716</v>
       </c>
     </row>
     <row r="577">
@@ -28269,10 +28269,10 @@
         <v>1.56</v>
       </c>
       <c r="I602" t="n">
-        <v>1.1985</v>
+        <v>1.199</v>
       </c>
       <c r="J602" t="n">
-        <v>27.5655</v>
+        <v>27.577</v>
       </c>
     </row>
     <row r="603">
@@ -28309,10 +28309,10 @@
         <v>1.25</v>
       </c>
       <c r="I603" t="n">
-        <v>0.6593</v>
+        <v>0.6597</v>
       </c>
       <c r="J603" t="n">
-        <v>15.1639</v>
+        <v>15.1731</v>
       </c>
     </row>
     <row r="604">
@@ -28349,10 +28349,10 @@
         <v>1.1</v>
       </c>
       <c r="I604" t="n">
-        <v>0.3181</v>
+        <v>0.3184</v>
       </c>
       <c r="J604" t="n">
-        <v>7.3163</v>
+        <v>7.3232</v>
       </c>
     </row>
     <row r="605">
@@ -28386,13 +28386,13 @@
         <v>23</v>
       </c>
       <c r="H605" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I605" t="n">
-        <v>0.237</v>
+        <v>0.2085</v>
       </c>
       <c r="J605" t="n">
-        <v>5.451</v>
+        <v>4.7955</v>
       </c>
     </row>
     <row r="606">
@@ -28429,10 +28429,10 @@
         <v>0.77</v>
       </c>
       <c r="I606" t="n">
-        <v>-0.6847</v>
+        <v>-0.6844</v>
       </c>
       <c r="J606" t="n">
-        <v>-15.7481</v>
+        <v>-15.7412</v>
       </c>
     </row>
     <row r="607">
@@ -28469,10 +28469,10 @@
         <v>1.4</v>
       </c>
       <c r="I607" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.7449</v>
       </c>
       <c r="J607" t="n">
-        <v>17.1465</v>
+        <v>17.1327</v>
       </c>
     </row>
     <row r="608">
@@ -28506,13 +28506,13 @@
         <v>23</v>
       </c>
       <c r="H608" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="I608" t="n">
-        <v>0.5925</v>
+        <v>0.6076</v>
       </c>
       <c r="J608" t="n">
-        <v>13.6275</v>
+        <v>13.9748</v>
       </c>
     </row>
     <row r="609">
@@ -28549,10 +28549,10 @@
         <v>1.06</v>
       </c>
       <c r="I609" t="n">
-        <v>0.1676</v>
+        <v>0.1673</v>
       </c>
       <c r="J609" t="n">
-        <v>3.8548</v>
+        <v>3.8479</v>
       </c>
     </row>
     <row r="610">
@@ -28589,10 +28589,10 @@
         <v>0.72</v>
       </c>
       <c r="I610" t="n">
-        <v>-0.3308</v>
+        <v>-0.3309</v>
       </c>
       <c r="J610" t="n">
-        <v>-7.6084</v>
+        <v>-7.6107</v>
       </c>
     </row>
     <row r="611">
@@ -28629,10 +28629,10 @@
         <v>0.61</v>
       </c>
       <c r="I611" t="n">
-        <v>-0.4299</v>
+        <v>-0.4301</v>
       </c>
       <c r="J611" t="n">
-        <v>-9.887700000000001</v>
+        <v>-9.892300000000001</v>
       </c>
     </row>
     <row r="612">
@@ -28666,13 +28666,13 @@
         <v>19</v>
       </c>
       <c r="H612" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I612" t="n">
-        <v>0.4209</v>
+        <v>0.4335</v>
       </c>
       <c r="J612" t="n">
-        <v>7.9971</v>
+        <v>8.236499999999999</v>
       </c>
     </row>
     <row r="613">
@@ -28709,10 +28709,10 @@
         <v>1</v>
       </c>
       <c r="I613" t="n">
-        <v>0.0072</v>
+        <v>0.0069</v>
       </c>
       <c r="J613" t="n">
-        <v>0.1368</v>
+        <v>0.1311</v>
       </c>
     </row>
     <row r="614">
@@ -28749,10 +28749,10 @@
         <v>0.82</v>
       </c>
       <c r="I614" t="n">
-        <v>-0.2259</v>
+        <v>-0.2261</v>
       </c>
       <c r="J614" t="n">
-        <v>-4.2921</v>
+        <v>-4.2959</v>
       </c>
     </row>
     <row r="615">
@@ -28789,10 +28789,10 @@
         <v>0.8</v>
       </c>
       <c r="I615" t="n">
-        <v>-0.2459</v>
+        <v>-0.246</v>
       </c>
       <c r="J615" t="n">
-        <v>-4.6721</v>
+        <v>-4.674</v>
       </c>
     </row>
     <row r="616">
@@ -28829,10 +28829,10 @@
         <v>0.78</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.2655</v>
+        <v>-0.2657</v>
       </c>
       <c r="J616" t="n">
-        <v>-5.0445</v>
+        <v>-5.0483</v>
       </c>
     </row>
     <row r="617">
@@ -28866,13 +28866,13 @@
         <v>19</v>
       </c>
       <c r="H617" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I617" t="n">
-        <v>0.8719</v>
+        <v>0.8633</v>
       </c>
       <c r="J617" t="n">
-        <v>16.5661</v>
+        <v>16.4027</v>
       </c>
     </row>
     <row r="618">
@@ -28906,13 +28906,13 @@
         <v>19</v>
       </c>
       <c r="H618" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I618" t="n">
-        <v>0.7084</v>
+        <v>0.6992</v>
       </c>
       <c r="J618" t="n">
-        <v>13.4596</v>
+        <v>13.2848</v>
       </c>
     </row>
     <row r="619">
@@ -28949,10 +28949,10 @@
         <v>1.02</v>
       </c>
       <c r="I619" t="n">
-        <v>0.0331</v>
+        <v>0.0335</v>
       </c>
       <c r="J619" t="n">
-        <v>0.6289</v>
+        <v>0.6365</v>
       </c>
     </row>
     <row r="620">
@@ -28989,10 +28989,10 @@
         <v>0.98</v>
       </c>
       <c r="I620" t="n">
-        <v>-0.0611</v>
+        <v>-0.0608</v>
       </c>
       <c r="J620" t="n">
-        <v>-1.1609</v>
+        <v>-1.1552</v>
       </c>
     </row>
     <row r="621">
@@ -29029,10 +29029,10 @@
         <v>0.86</v>
       </c>
       <c r="I621" t="n">
-        <v>-0.2104</v>
+        <v>-0.2102</v>
       </c>
       <c r="J621" t="n">
-        <v>-3.9976</v>
+        <v>-3.9938</v>
       </c>
     </row>
     <row r="622">
@@ -30269,10 +30269,10 @@
         <v>1.29</v>
       </c>
       <c r="I652" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6096</v>
       </c>
       <c r="J652" t="n">
-        <v>12.8184</v>
+        <v>12.8016</v>
       </c>
     </row>
     <row r="653">
@@ -30306,13 +30306,13 @@
         <v>21</v>
       </c>
       <c r="H653" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I653" t="n">
-        <v>0.3118</v>
+        <v>0.3304</v>
       </c>
       <c r="J653" t="n">
-        <v>6.5478</v>
+        <v>6.9384</v>
       </c>
     </row>
     <row r="654">
@@ -30349,10 +30349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I654" t="n">
-        <v>-0.0931</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J654" t="n">
-        <v>-1.9551</v>
+        <v>-1.9593</v>
       </c>
     </row>
     <row r="655">
@@ -30389,10 +30389,10 @@
         <v>0.75</v>
       </c>
       <c r="I655" t="n">
-        <v>-0.2924</v>
+        <v>-0.2926</v>
       </c>
       <c r="J655" t="n">
-        <v>-6.1404</v>
+        <v>-6.1446</v>
       </c>
     </row>
     <row r="656">
@@ -30429,10 +30429,10 @@
         <v>0.45</v>
       </c>
       <c r="I656" t="n">
-        <v>-0.5582</v>
+        <v>-0.5584</v>
       </c>
       <c r="J656" t="n">
-        <v>-11.7222</v>
+        <v>-11.7264</v>
       </c>
     </row>
     <row r="657">
@@ -30669,10 +30669,10 @@
         <v>1.4</v>
       </c>
       <c r="I662" t="n">
-        <v>0.5976</v>
+        <v>0.597</v>
       </c>
       <c r="J662" t="n">
-        <v>14.3424</v>
+        <v>14.328</v>
       </c>
     </row>
     <row r="663">
@@ -30709,10 +30709,10 @@
         <v>1.19</v>
       </c>
       <c r="I663" t="n">
-        <v>0.3328</v>
+        <v>0.3324</v>
       </c>
       <c r="J663" t="n">
-        <v>7.9872</v>
+        <v>7.9776</v>
       </c>
     </row>
     <row r="664">
@@ -30749,10 +30749,10 @@
         <v>0.91</v>
       </c>
       <c r="I664" t="n">
-        <v>-0.1326</v>
+        <v>-0.1328</v>
       </c>
       <c r="J664" t="n">
-        <v>-3.1824</v>
+        <v>-3.1872</v>
       </c>
     </row>
     <row r="665">
@@ -30786,13 +30786,13 @@
         <v>24</v>
       </c>
       <c r="H665" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I665" t="n">
-        <v>-0.3261</v>
+        <v>-0.3169</v>
       </c>
       <c r="J665" t="n">
-        <v>-7.8264</v>
+        <v>-7.6056</v>
       </c>
     </row>
     <row r="666">
@@ -30829,10 +30829,10 @@
         <v>0.61</v>
       </c>
       <c r="I666" t="n">
-        <v>-0.4256</v>
+        <v>-0.4257</v>
       </c>
       <c r="J666" t="n">
-        <v>-10.2144</v>
+        <v>-10.2168</v>
       </c>
     </row>
     <row r="667">
